--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1114,7 +1114,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -10306,7 +10305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10337,7 +10336,7 @@
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
         <is>
-          <t>Tally: 17 bug findings -&gt; 10 Fixed, 6 Flagged (product decisions), 1 Disproven. Plus 11 test-infra/wiring items (INF-*).</t>
+          <t>Tally: 17 bug findings -&gt; 10 Fixed, 6 Flagged (product decisions), 1 Disproven. Plus 14 test-infra/wiring items (INF-*): 13 Fixed, 1 Open (INF-14).</t>
         </is>
       </c>
     </row>
@@ -11671,6 +11670,147 @@
       <c r="F32" t="inlineStr">
         <is>
           <t>Fixed -- pluralised the countable nouns (optional trailing s) across the finance/sales/procurement/ops/hr intent patterns (services/ai/brain_rbac.py); plural finance/sales/procurement/ops questions now classify deterministically. Regression-guarded in test_s9_ai_logic.py (test_bug17_plural_finance_questions_are_gated).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>INF-12</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Test infra</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>12 single-process DB tests (skip under xdist)</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>12 tests that skip under xdist (rebind module db globals) had gone red unseen behind the green parallel run; all 12 already failed before 9effa23. Every one was STALE -- product behaviour changed on purpose -- not a regression: (1) test_workflow_counts x2: user had no role; since the 2026-10-03 RBAC audit a member is scoped to their team's pipelines (workflow_scope), which also read the unpatched core.db. (2) test_workflow_is_continuous race x2: advance_workflow now 404s a card that is not there (_in_my_pipelines, 2026-10-03) and the tests never inserted one. (3) test_ops_says_how_long_work_takes x3: 53157b2 'Late means late' counts open past-due work as late (67%-&gt;50%, dated 3-&gt;4) and added late_open; the page now passes approvals= to WorkMovesRow. (4) test_journey1_score_cache: 53157b2 added the period to the cache key (t:1 -&gt; t:1:all). (5) test_ops_names_the_jam: 'fresh' card hard-coded to 2026-09-28 aged into a real jam (2-day stage) -- date-dependent test. (6) test_rbac_p0_access x2: the 2026-09-24 buyer/supplier CRM split (J7-04/J8-01, J14-05) replaced require_perm('people') with require_crm / may_see_contact; J14-13 makes approvals imply captures_approve. (7) test_second_company owner gate: auth.me takes (request, response, user) since B27 2026-09-29.</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>Fixed (tests updated to the deliberate behaviour; no app code changed) -- owner user for counts; card inserted before the race; 50% / dated 4 / late_open 1; cache key t:1:all; 'fresh' = yesterday in IST via shared.workdays.today_ist; CRM wiring asserts require_crm or may_see_contact; captures_approve expected; me() called with a starlette Request + Response under e2e_env. 12/12 green single-process; tripwire run shows 0 real-DB access from them.</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>80cd2bf (picked up by a parallel commit) + 2026-10-06 follow-up</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>test_workflow_counts, test_workflow_is_continuous, test_ops_says_how_long_work_takes, test_journey1_score_cache, test_ops_names_the_jam, test_rbac_p0_access, test_second_company</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>T10-11.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>INF-13</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Safety / test infra</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>e2e_harness: /auth/me setup claim</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>GET /auth/me calls services.ai.ai_setup.claim_setup_backfill (9effa23), and ai_setup binds its own db that e2e_env never rebound -- so every in-process /me reached the PRODUCTION client from a test, and the 'Cannot use AsyncMongoClient in different event loop' error followed whichever test touched it second. Same class: test_ai_keys_stay_on_the_server::test_a_settings_save_answers_without_the_keys rebound only routers.tenant_settings, so the save's core.log_activity wrote an activity row through the real client (order-dependent failure).</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>Fixed -- services.ai.ai_setup added to e2e_harness._DB_MODULES and its _backfill_missing_setup (three LLM calls) neutralised as a fire-and-forget writer; the settings-save test runs under e2e_env. Verified with a tripwire plugin that swaps the real db for a recorder before collection: 0 hits from the fixed files.</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>80cd2bf (harness) + 2026-10-06 follow-up</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>tests/e2e_harness.py, test_ai_keys_stay_on_the_server.py</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>T10-11.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>INF-14</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Safety / test infra</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>test_second_company register tests</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Found by the same tripwire, PRE-EXISTING and passing: five register tests in test_second_company.py (needs_no_email..., first_company_sets_no_password..., signed_in_founder..., keeps_a_contact_address..., address_can_be_skipped...) make REAL LLM calls and write ai_calls / usage_events / platform_alerts / tenants through the real client; test_whatsapp_lands_in_the_company_the_number_chose reads users from it. They rebind only routers.auth/core.</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>Open -- split out as its own task (run under e2e_env, stub the onboarding generators, extend _DB_MODULES; confirm 0 tripwire hits).</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>test_second_company.py</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>T10-11.2</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -11,8 +11,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backlog" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug Log" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Audit 2026-10-08" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Product Audit 2026-10-08'!$A$4:$I$74</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,8 +95,15 @@
       <color rgb="00374151"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -130,6 +140,31 @@
         <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F4F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE2E2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -157,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -201,6 +236,27 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1081,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1114,6 +1170,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1577,6 +1634,43 @@
       <c r="G18" s="12" t="inlineStr">
         <is>
           <t>Testing = frontend AS WELL AS backend. Drive the REAL UI in the browser preview: every button/form/nav/state, role-gated UI, responsive/mobile, empty/loading/error states, console+network health, the karma design-system, and the founder 'feeling'. Every functional + E2E scenario also gets a browser-driven variant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>Audit</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Product audit 2026-10-08</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>70 findings (58 to act on) in the "Product Audit 2026-10-08" sheet. Batch 1 done 2026-10-08: B-02 + C-20 one department list (the teams), D-01 Settings crash for members, A-01 sign-up resume, B-04 + C-01 plan card (trial, upgrade, AI allowance, one seat count), A-16 bring your team in.</t>
         </is>
       </c>
     </row>
@@ -11817,4 +11911,3136 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I74"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>Epic 10 -- Product audit (2026-10-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>End-to-end walk of the whole product in the browser, sign-up to every section, as owner / HR / Accounts / Sales, on the scratch DB dos_engine_0921c (messaging off). Findings only; full write-up: docs/audit/2026-10-08-e2e-product-audit.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>Tally: P0 2 / P1 11 / P2 29 / P3 16 / Info 12 = 70 findings</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Sev</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>Where</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>What happened</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>What should happen</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>Work group</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I4" s="20" t="inlineStr">
+        <is>
+          <t>Notes / fix</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>A-01</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up, resume after reload</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>Reloaded on step 02 ("And your name?", left empty). The page said "Welcome back — we kept your answers" and resumed at step 03 (company name), skipping the unanswered name step. Back showed the name still empty.</t>
+        </is>
+      </c>
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>Resume at the first step with a missing answer, never past it.</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>4. Fix the bugs found (P1)</t>
+        </is>
+      </c>
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push). Signup.js resume scans answers in the wizard's own order (phone, name, company, email, team size). Live: reload on a blank "And your name?" reopens on step 02 with "Welcome back".</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>A-02</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up, browser Back</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>The browser's Back button on a sign-up step leaves sign-up entirely (it went to /login); the steps are not in the browser history.</t>
+        </is>
+      </c>
+      <c r="F6" s="26" t="inlineStr">
+        <is>
+          <t>Back moves to the previous step (push each step into history), or the in-page Back is the only way and the browser Back confirms before leaving.</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="inlineStr">
+        <is>
+          <t>9. Smaller product gaps (P2)</t>
+        </is>
+      </c>
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>A-03</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in, mobile tab</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>An unregistered number gets "No account is registered with this mobile number". Anyone can test which numbers have accounts (account enumeration). The email tab correctly says "Invalid email or password" for both cases.</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>Same reply either way ("If this number has an account, we've sent a code"), with "Start a new company" offered.</t>
+        </is>
+      </c>
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>7. Trust and privacy (P2)</t>
+        </is>
+      </c>
+      <c r="H7" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I7" s="26" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>A-04</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up, mobile</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>"Enter a 10-digit Indian mobile number" — only Indian numbers are accepted.</t>
+        </is>
+      </c>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>Country code picker, at least for Gulf, UK, US, Singapore (export SMEs work with them).</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t>9. Smaller product gaps (P2)</t>
+        </is>
+      </c>
+      <c r="H8" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>A-05</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in, email</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>name@example.test (a valid address shape) is refused as "That email address does not look right". Only reserved test domains hit this, but the message is wrong for a valid-looking address.</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>Low priority; message could say the domain can't receive mail.</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>A-06</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up / sign-in wording</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>"Incorrect OTP", "Send OTP", "Mobile OTP" while the same screens say "code". No count of attempts left after a wrong code.</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>"That code isn't right - 4 tries left." Use "code" everywhere.</t>
+        </is>
+      </c>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>A-07</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>Login footer</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>"Workflow as an engine · Decision Desk · Dex" — internal names on the first screen a visitor sees.</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>A plain promise ("Your team's work and decisions in one place").</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>A-08</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up code entry (to re-check on a phone)</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>Typing the six digits fast (automated typing) submitted a wrong code once; filling all six at once (SMS autofill) worked. Possibly an automation artefact.</t>
+        </is>
+      </c>
+      <c r="F12" s="26" t="inlineStr">
+        <is>
+          <t>Re-check by hand on Android/iPhone with a fast typist.</t>
+        </is>
+      </c>
+      <c r="G12" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>A-09</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up, existing number</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>A number that already owns a company can start sign-up again (allowed: one person, many companies) — checked further below.</t>
+        </is>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>Works - no action</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>A-10</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up interview, reload</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>Reloaded at question 3 of the interview: it went back to the language picker and then restarted at question 1. Both typed answers were lost (the steps before it were kept).</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>Keep interview answers in the draft like every other step; resume at the next question.</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t>9. Smaller product gaps (P2)</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>A-11</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up, "Here's how Audit Textiles will run"</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>The review shows teams and recurring tasks only. The approval rules given in the interview (orders over ₹5 lakh, discounts over 5%, rework over ₹50,000, peak-season leave to the owner, HR manager approves leave) and the order pipeline are not shown, so the owner cannot check them before entering.</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>Show "Approvals" and "How an order moves" sections in the review, each editable.</t>
+        </is>
+      </c>
+      <c r="G15" s="26" t="inlineStr">
+        <is>
+          <t>3. Make the setup match what the founder said (P1)</t>
+        </is>
+      </c>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>A-12</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up review</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>After "Add a workflow" the counter said 9 recurring tasks but 8 were listed; "Monthly export invoice reconciliation" disappeared from the list.</t>
+        </is>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>Counter and list agree; say when an earlier item was replaced.</t>
+        </is>
+      </c>
+      <c r="G16" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>A-13</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up review</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>The six department chips are stacked one per line in a wide card.</t>
+        </is>
+      </c>
+      <c r="F17" s="26" t="inlineStr">
+        <is>
+          <t>Chips wrap across the card.</t>
+        </is>
+      </c>
+      <c r="G17" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H17" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I17" s="26" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>A-14</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up interview</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>A "Why we ask" line read "Reveals founder's real daily touchpoints and approval habit" — internal wording, about the person in the third person.</t>
+        </is>
+      </c>
+      <c r="F18" s="26" t="inlineStr">
+        <is>
+          <t>Address them: "So Dex knows what you check each week."</t>
+        </is>
+      </c>
+      <c r="G18" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H18" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I18" s="26" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>A-15</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up interview language</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>The interview offers 11 languages; the app itself is English, Hindi and Tamil only (checked in i18n). A founder who interviews in Bengali lands in an English app with no warning.</t>
+        </is>
+      </c>
+      <c r="F19" s="26" t="inlineStr">
+        <is>
+          <t>Say "the app is in English, Hindi or Tamil for now", or narrow the list, or carry the choice into the app language where it exists.</t>
+        </is>
+      </c>
+      <c r="G19" s="26" t="inlineStr">
+        <is>
+          <t>9. Smaller product gaps (P2)</t>
+        </is>
+      </c>
+      <c r="H19" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>A-16</t>
+        </is>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>After sign-up</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>No step invites the team, and the first screens (welcome card, Desk empty state) never mention it. A company of one gets little from the product.</t>
+        </is>
+      </c>
+      <c r="F20" s="26" t="inlineStr">
+        <is>
+          <t>A "Bring your team in" step at the end of sign-up and a Desk card until the first person is invited.</t>
+        </is>
+      </c>
+      <c r="G20" s="26" t="inlineStr">
+        <is>
+          <t>5. Getting a team in (P1/P2)</t>
+        </is>
+      </c>
+      <c r="H20" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I20" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push). Desk "Bring your team in" card (pages/desk/TeamNudge.jsx) for whoever can add people, until anyone else is active or invited; "Later" hides it 3 days. /team?add=1 opens Add member. End of sign-up: "Enter and bring my team in first" lands on Add member. Live on a one-person company: shows on phone (375x812, no scroll) and desktop; Later persists; Audit Textiles (4 people) does not show it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>A-17</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="inlineStr">
+        <is>
+          <t>Desk empty state</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>The example decision is "Tell Suresh to ship the indigo lot before Friday" — Suresh is not in this company.</t>
+        </is>
+      </c>
+      <c r="F21" s="26" t="inlineStr">
+        <is>
+          <t>Use one of the company's own department names, or a neutral example.</t>
+        </is>
+      </c>
+      <c r="G21" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H21" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I21" s="26" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>A-18</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="inlineStr">
+        <is>
+          <t>Website step</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>A bad address ("hello world") falls back gracefully to two manual questions; the server-side fetch has an SSRF guard (services/ssrf_guard.py).</t>
+        </is>
+      </c>
+      <c r="F22" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="26" t="inlineStr">
+        <is>
+          <t>Works - no action</t>
+        </is>
+      </c>
+      <c r="I22" s="26" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>A-19</t>
+        </is>
+      </c>
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D23" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up review</t>
+        </is>
+      </c>
+      <c r="E23" s="26" t="inlineStr">
+        <is>
+          <t>"Add a workflow" worked well: one typed sentence added the QC-agent inspection and the discount rule to the summary. The interview questions were specific and good.</t>
+        </is>
+      </c>
+      <c r="F23" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="26" t="inlineStr">
+        <is>
+          <t>Works - no action</t>
+        </is>
+      </c>
+      <c r="I23" s="26" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>A-20</t>
+        </is>
+      </c>
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D24" s="26" t="inlineStr">
+        <is>
+          <t>After sign-up</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr">
+        <is>
+          <t>What sign-up built is genuinely good: 4 pipelines (Order Fulfillment, Raw Material Procurement, Buyer Sampling, Workforce Management) with 3 concrete tasks per stage on the right team, tailored expense/asset categories, vocabulary (Buyer / Supplier) and the product filled in.</t>
+        </is>
+      </c>
+      <c r="F24" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="26" t="inlineStr">
+        <is>
+          <t>Works - no action</t>
+        </is>
+      </c>
+      <c r="I24" s="26" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>B-01</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>Interview → setup</t>
+        </is>
+      </c>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>None of the interview's approval rules reached the setup. Sales confirming orders up to ₹5 lakh became "Order Confirmed: only the owner can advance" (the owner must confirm every order). Leave approver stayed "Owner (default)" for every team, though the HR manager was named. The high-value threshold is a generic ₹50,000 (₹1 lakh POs and ₹5 lakh orders were given). Rework over ₹50,000 and discounts over 5% went nowhere. "Peak-season leave approval" became a recurring task instead of a rule.</t>
+        </is>
+      </c>
+      <c r="F25" s="26" t="inlineStr">
+        <is>
+          <t>Interview answers about who approves what become approval settings, shown on the review screen (A-11) for the owner to confirm.</t>
+        </is>
+      </c>
+      <c r="G25" s="26" t="inlineStr">
+        <is>
+          <t>3. Make the setup match what the founder said (P1)</t>
+        </is>
+      </c>
+      <c r="H25" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I25" s="26" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>B-02</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>Settings → Team, Business, Operations</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>Three different "department" lists with different names: Teams (Sales &amp; Buyer Management, Production, Quality, Logistics &amp; Shipping, Accounts, HR), Business vocabulary "task type / department labels" (Operations, Sales &amp; Buyer, Procurement, Production, Accounts, HR) and Operations "task categories" (Buyer Coordination, Production, Quality Control, Logistics &amp; Shipping, Finance &amp; Accounts, Inventory &amp; Materials, HR &amp; Workforce). An owner cannot tell which one decides what.</t>
+        </is>
+      </c>
+      <c r="F26" s="26" t="inlineStr">
+        <is>
+          <t>One list of teams; categories, if kept, clearly named as task kinds and derived from it.</t>
+        </is>
+      </c>
+      <c r="G26" s="26" t="inlineStr">
+        <is>
+          <t>3. Make the setup match what the founder said (P1)</t>
+        </is>
+      </c>
+      <c r="H26" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I26" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push). One list = the teams. services/task_departments.py: a task's department is a team key; Dex is given the teams (voice.py); New Task "Department" + My Work tabs read tenant.roles (lib/operatingModel.teamCategories); Operations category editor replaced by a pointer to Team &amp; access; dead Business-vocabulary task-type labels removed; stage/routine tasks fall back to their team (_derive_task_type); finance follow-ups filed under the accounts team. One-time migration task_types_follow_teams_v1 moves old category keys onto the team they mean (resolve_role). Live: Audit Textiles task list = 7 teams; all tasks on team keys.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>B-03</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>Operations → stage approvals</t>
+        </is>
+      </c>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>An approval to leave a stage is yes/no per stage. There is no "only above ₹X" condition, so "sales confirms up to ₹5 lakh, owner above" cannot be set.</t>
+        </is>
+      </c>
+      <c r="F27" s="26" t="inlineStr">
+        <is>
+          <t>Value-based approval on a stage (amount on the card ≥ threshold → owner).</t>
+        </is>
+      </c>
+      <c r="G27" s="26" t="inlineStr">
+        <is>
+          <t>3. Make the setup match what the founder said (P1)</t>
+        </is>
+      </c>
+      <c r="H27" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I27" s="26" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>B-04</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>Workspace → Plan and seats</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
+        <is>
+          <t>"Trial · ends 22 Oct 2026 · 1 of 10 seats used" — no upgrade or payment, and nothing says what happens on the 22nd. The monthly AI allowance (300,000 trial tokens) is not shown anywhere; the owner learns it ran out when AI stops.</t>
+        </is>
+      </c>
+      <c r="F28" s="26" t="inlineStr">
+        <is>
+          <t>Upgrade (Razorpay), what the trial end means, and an AI-use meter with the reset date.</t>
+        </is>
+      </c>
+      <c r="G28" s="26" t="inlineStr">
+        <is>
+          <t>6. Trial, plan and AI allowance (P1)</t>
+        </is>
+      </c>
+      <c r="H28" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I28" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push). /tenant/plan now returns ai_allowance {used, cap, percent, over, resets_on}, trial_days_left, billing_configured. New Settings PlanCard: trial line ("14 days left... choose a plan before then"), seats bar, AI-this-month bar with reset date and a warning at 90%/over, "Choose a plan" -&gt; plan picker -&gt; POST /billing/checkout (Razorpay hand-off); where online payment is not configured, "Email us" (support@decisionos.biz). OPEN DECISION: nothing is enforced when a trial ends (no read-only mode) - product call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>B-05</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>Workspace → AI and WhatsApp keys</t>
+        </is>
+      </c>
+      <c r="E29" s="26" t="inlineStr">
+        <is>
+          <t>Offers the company's own Anthropic / Gemini / OpenAI / Sarvam / Voyage keys and a WhatsApp Business token. Per the AI audit (AB-02) the WhatsApp token is never used, and company AI keys are not used at runtime either. The card promises what does not happen.</t>
+        </is>
+      </c>
+      <c r="F29" s="26" t="inlineStr">
+        <is>
+          <t>Hide it until per-company keys/WhatsApp are real (AB-02 / AB-04).</t>
+        </is>
+      </c>
+      <c r="G29" s="26" t="inlineStr">
+        <is>
+          <t>6. Trial, plan and AI allowance (P1)</t>
+        </is>
+      </c>
+      <c r="H29" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I29" s="26" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>B-06</t>
+        </is>
+      </c>
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D30" s="26" t="inlineStr">
+        <is>
+          <t>Business → Company details</t>
+        </is>
+      </c>
+      <c r="E30" s="26" t="inlineStr">
+        <is>
+          <t>Company mobile and email are empty though sign-up collected both; Region is empty though the interview said Tiruppur.</t>
+        </is>
+      </c>
+      <c r="F30" s="26" t="inlineStr">
+        <is>
+          <t>Pre-fill from sign-up.</t>
+        </is>
+      </c>
+      <c r="G30" s="26" t="inlineStr">
+        <is>
+          <t>3. Make the setup match what the founder said (P1)</t>
+        </is>
+      </c>
+      <c r="H30" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I30" s="26" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>B-07</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="inlineStr">
+        <is>
+          <t>Business → "WhatsApp workspace code"</t>
+        </is>
+      </c>
+      <c r="E31" s="26" t="inlineStr">
+        <is>
+          <t>Shows the company's internal ID with "share this with your WhatsApp integrator… so messages from unknown numbers land in this workspace" — internal plumbing, tied to the WA_TENANT_ID routing (AB-01).</t>
+        </is>
+      </c>
+      <c r="F31" s="26" t="inlineStr">
+        <is>
+          <t>Remove until per-company WhatsApp exists.</t>
+        </is>
+      </c>
+      <c r="G31" s="26" t="inlineStr">
+        <is>
+          <t>6. Trial, plan and AI allowance (P1)</t>
+        </is>
+      </c>
+      <c r="H31" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I31" s="26" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>B-08</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D32" s="26" t="inlineStr">
+        <is>
+          <t>Account → Password</t>
+        </is>
+      </c>
+      <c r="E32" s="26" t="inlineStr">
+        <is>
+          <t>"You sign in with your mobile… there's no password", yet the login page has an Email &amp; Password tab a new owner can never use. If the phone or SMS fails there is no way in.</t>
+        </is>
+      </c>
+      <c r="F32" s="26" t="inlineStr">
+        <is>
+          <t>Let an owner set a password (or a backup sign-in), or drop the email tab for OTP-only accounts.</t>
+        </is>
+      </c>
+      <c r="G32" s="26" t="inlineStr">
+        <is>
+          <t>7. Trust and privacy (P2)</t>
+        </is>
+      </c>
+      <c r="H32" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I32" s="26" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>B-09</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t>Team &amp; access → HR defaults</t>
+        </is>
+      </c>
+      <c r="E33" s="26" t="inlineStr">
+        <is>
+          <t>HR can approve leave but has Manage Team off, so the HR manager cannot add or edit employees.</t>
+        </is>
+      </c>
+      <c r="F33" s="26" t="inlineStr">
+        <is>
+          <t>HR gets Manage Team by default (or offer it when creating the HR team).</t>
+        </is>
+      </c>
+      <c r="G33" s="26" t="inlineStr">
+        <is>
+          <t>5. Getting a team in (P1/P2)</t>
+        </is>
+      </c>
+      <c r="H33" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I33" s="26" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>B-10</t>
+        </is>
+      </c>
+      <c r="B34" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D34" s="26" t="inlineStr">
+        <is>
+          <t>Team &amp; access → What owners can open</t>
+        </is>
+      </c>
+      <c r="E34" s="26" t="inlineStr">
+        <is>
+          <t>Areas can be switched off for "all owners, you included" — a single owner can switch off Finance for themselves. Not tried here (to avoid locking the test company); worth a guard.</t>
+        </is>
+      </c>
+      <c r="F34" s="26" t="inlineStr">
+        <is>
+          <t>Warn when the only owner switches an area off for themselves; keep a way back.</t>
+        </is>
+      </c>
+      <c r="G34" s="26" t="inlineStr">
+        <is>
+          <t>7. Trust and privacy (P2)</t>
+        </is>
+      </c>
+      <c r="H34" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I34" s="26" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>B-11</t>
+        </is>
+      </c>
+      <c r="B35" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D35" s="26" t="inlineStr">
+        <is>
+          <t>Team &amp; access → add team</t>
+        </is>
+      </c>
+      <c r="E35" s="26" t="inlineStr">
+        <is>
+          <t>A duplicate team name says "A role with this name already exists" (the screen says team). Adding a team gives no confirmation.</t>
+        </is>
+      </c>
+      <c r="F35" s="26" t="inlineStr">
+        <is>
+          <t>"There's already a Production team." / "Design &amp; Sampling added."</t>
+        </is>
+      </c>
+      <c r="G35" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H35" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I35" s="26" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>B-12</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="inlineStr">
+        <is>
+          <t>Settings — missing for an Indian SME</t>
+        </is>
+      </c>
+      <c r="E36" s="26" t="inlineStr">
+        <is>
+          <t>Not found anywhere: GST rates and invoice numbering; bank details and logo on invoices; default payment terms; financial year (Apr–Mar); working days / holidays (the "stuck after N working days" rule needs them); leave types and balances; notification preferences (email / WhatsApp / push); integrations (Tally, Zoho Books, Google).</t>
+        </is>
+      </c>
+      <c r="F36" s="26" t="inlineStr">
+        <is>
+          <t>Decide which belong in v1; GST/invoice basics and leave types are the most asked for.</t>
+        </is>
+      </c>
+      <c r="G36" s="26" t="inlineStr">
+        <is>
+          <t>9. Smaller product gaps (P2)</t>
+        </is>
+      </c>
+      <c r="H36" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I36" s="26" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>B-13</t>
+        </is>
+      </c>
+      <c r="B37" s="29" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="E37" s="26" t="inlineStr">
+        <is>
+          <t>Good: audit log, AI processing switch with who agreed and when, deadline escalation (warn N days before, manager after N, owner after N), approval handover while away, delete account with "what we hold".</t>
+        </is>
+      </c>
+      <c r="F37" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" s="26" t="inlineStr">
+        <is>
+          <t>Works - no action</t>
+        </is>
+      </c>
+      <c r="I37" s="26" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>C-01</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="inlineStr">
+        <is>
+          <t>Team vs Settings</t>
+        </is>
+      </c>
+      <c r="E38" s="26" t="inlineStr">
+        <is>
+          <t>Team page says "1 of 15 seats"; Settings → Plan says "1 of 10 seats used".</t>
+        </is>
+      </c>
+      <c r="F38" s="26" t="inlineStr">
+        <is>
+          <t>One number from one source.</t>
+        </is>
+      </c>
+      <c r="G38" s="26" t="inlineStr">
+        <is>
+          <t>6. Trial, plan and AI allowance (P1)</t>
+        </is>
+      </c>
+      <c r="H38" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I38" s="26" t="inlineStr">
+        <is>
+          <t>FIXED with B-04: Settings now shares Team's ["tenant-plan"] query (one source). Live both read "4 of 15". The "1 of 10" seen in the audit could not be reproduced from code or data (tenant has no seat override; trial = 15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>C-02</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D39" s="26" t="inlineStr">
+        <is>
+          <t>Add member → "They will see these menus"</t>
+        </is>
+      </c>
+      <c r="E39" s="26" t="inlineStr">
+        <is>
+          <t>For an HR member the preview lists CRM and "Finance (upload only)", while HR's access has CRM and Finance off (her profile says "No access to … CRM … Finance"). To confirm when signed in as HR (section D).</t>
+        </is>
+      </c>
+      <c r="F39" s="26" t="inlineStr">
+        <is>
+          <t>The preview matches the access.</t>
+        </is>
+      </c>
+      <c r="G39" s="26" t="inlineStr">
+        <is>
+          <t>5. Getting a team in (P1/P2)</t>
+        </is>
+      </c>
+      <c r="H39" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I39" s="26" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>C-03</t>
+        </is>
+      </c>
+      <c r="B40" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="inlineStr">
+        <is>
+          <t>Team tree vs profile</t>
+        </is>
+      </c>
+      <c r="E40" s="26" t="inlineStr">
+        <is>
+          <t>The tree draws all three members under Meera; each profile says "Reports to: No one". The coloured dot on invited members has no legend.</t>
+        </is>
+      </c>
+      <c r="F40" s="26" t="inlineStr">
+        <is>
+          <t>Same answer in both; label "Invited".</t>
+        </is>
+      </c>
+      <c r="G40" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H40" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I40" s="26" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>C-04</t>
+        </is>
+      </c>
+      <c r="B41" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D41" s="26" t="inlineStr">
+        <is>
+          <t>Add member</t>
+        </is>
+      </c>
+      <c r="E41" s="26" t="inlineStr">
+        <is>
+          <t>Nothing is sent to the new member, even with an email given; the owner must share the link. Clear on screen, but an email invite would save a step. Duplicate email says only "Email already registered" (duplicate phones name the person).</t>
+        </is>
+      </c>
+      <c r="F41" s="26" t="inlineStr">
+        <is>
+          <t>Optional email invite; say whose email it is.</t>
+        </is>
+      </c>
+      <c r="G41" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H41" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I41" s="26" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>C-05</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D42" s="26" t="inlineStr">
+        <is>
+          <t>CRM → buyer</t>
+        </is>
+      </c>
+      <c r="E42" s="26" t="inlineStr">
+        <is>
+          <t>The same buyer name can be added twice with no warning ("Northwind Apparel" ×2).</t>
+        </is>
+      </c>
+      <c r="F42" s="26" t="inlineStr">
+        <is>
+          <t>"There's already a buyer called Northwind Apparel - open it?"</t>
+        </is>
+      </c>
+      <c r="G42" s="26" t="inlineStr">
+        <is>
+          <t>9. Smaller product gaps (P2)</t>
+        </is>
+      </c>
+      <c r="H42" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I42" s="26" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>C-06</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D43" s="26" t="inlineStr">
+        <is>
+          <t>CRM → GSTIN</t>
+        </is>
+      </c>
+      <c r="E43" s="26" t="inlineStr">
+        <is>
+          <t>"ABC123" is accepted as a GSTIN.</t>
+        </is>
+      </c>
+      <c r="F43" s="26" t="inlineStr">
+        <is>
+          <t>Validate the 15-character GSTIN format (and state code).</t>
+        </is>
+      </c>
+      <c r="G43" s="26" t="inlineStr">
+        <is>
+          <t>9. Smaller product gaps (P2)</t>
+        </is>
+      </c>
+      <c r="H43" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I43" s="26" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>C-07</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D44" s="26" t="inlineStr">
+        <is>
+          <t>CRM → export buyer</t>
+        </is>
+      </c>
+      <c r="E44" s="26" t="inlineStr">
+        <is>
+          <t>No country, currency, payment terms, credit limit or multiple contact people on a contact; a UK buyer's page shows money in ₹.</t>
+        </is>
+      </c>
+      <c r="F44" s="26" t="inlineStr">
+        <is>
+          <t>Country + currency + payment terms on the contact; amounts in that currency.</t>
+        </is>
+      </c>
+      <c r="G44" s="26" t="inlineStr">
+        <is>
+          <t>9. Smaller product gaps (P2)</t>
+        </is>
+      </c>
+      <c r="H44" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I44" s="26" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>C-08</t>
+        </is>
+      </c>
+      <c r="B45" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="inlineStr">
+        <is>
+          <t>CRM wording</t>
+        </is>
+      </c>
+      <c r="E45" s="26" t="inlineStr">
+        <is>
+          <t>The contact page labels the buyer "Customer" and the empty state says "a customer, a partner or a supplier" although the company's word is Buyer. Delete sits inside Edit only.</t>
+        </is>
+      </c>
+      <c r="F45" s="26" t="inlineStr">
+        <is>
+          <t>Use the vocabulary everywhere; a visible Delete in the page menu.</t>
+        </is>
+      </c>
+      <c r="G45" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H45" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I45" s="26" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>C-09</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="inlineStr">
+        <is>
+          <t>Workflows → advance / create</t>
+        </is>
+      </c>
+      <c r="E46" s="26" t="inlineStr">
+        <is>
+          <t>Creating a card and advancing a stage each took ~4–10 s with no spinner or "Moving…" state; the create form stayed open with no feedback.</t>
+        </is>
+      </c>
+      <c r="F46" s="26" t="inlineStr">
+        <is>
+          <t>A busy state on the button; close the form at once and show the card as "saving".</t>
+        </is>
+      </c>
+      <c r="G46" s="26" t="inlineStr">
+        <is>
+          <t>8. Speed and feedback (P2)</t>
+        </is>
+      </c>
+      <c r="H46" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I46" s="26" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>C-10</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>Workflows → "Move on" dialog</t>
+        </is>
+      </c>
+      <c r="E47" s="26" t="inlineStr">
+        <is>
+          <t>Tasks set to require evidence (Settings shows "evidence" on each stage task) can be closed as "It was done — close it" from the move dialog with no proof.</t>
+        </is>
+      </c>
+      <c r="F47" s="26" t="inlineStr">
+        <is>
+          <t>Ask for the proof, or mark them "done without proof".</t>
+        </is>
+      </c>
+      <c r="G47" s="26" t="inlineStr">
+        <is>
+          <t>4. Fix the bugs found (P1)</t>
+        </is>
+      </c>
+      <c r="H47" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I47" s="26" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>C-11</t>
+        </is>
+      </c>
+      <c r="B48" s="29" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="inlineStr">
+        <is>
+          <t>Workflows</t>
+        </is>
+      </c>
+      <c r="E48" s="26" t="inlineStr">
+        <is>
+          <t>Good: the board, auto-created stage tasks, stage due dates and target date, and the "Move on? say what happens to each open task (Done / Not needed / Keep)" dialog. The server refuses an advance with open tasks.</t>
+        </is>
+      </c>
+      <c r="F48" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" s="26" t="inlineStr">
+        <is>
+          <t>Works - no action</t>
+        </is>
+      </c>
+      <c r="I48" s="26" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>C-12</t>
+        </is>
+      </c>
+      <c r="B49" s="29" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D49" s="26" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="E49" s="26" t="inlineStr">
+        <is>
+          <t>Good: delete asks first and explains what stays as history; Import from spreadsheet exists; duplicate phone/email are blocked when adding team members.</t>
+        </is>
+      </c>
+      <c r="F49" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" s="26" t="inlineStr">
+        <is>
+          <t>Works - no action</t>
+        </is>
+      </c>
+      <c r="I49" s="26" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="24" t="inlineStr">
+        <is>
+          <t>C-13</t>
+        </is>
+      </c>
+      <c r="B50" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D50" s="26" t="inlineStr">
+        <is>
+          <t>Decisions (Dex) → task due date</t>
+        </is>
+      </c>
+      <c r="E50" s="26" t="inlineStr">
+        <is>
+          <t>Decision said "Rahul to send the revised pro-forma invoice by Friday" (today Thu 8 Oct, so Fri 9 Oct). The task was created due Mon 12 Oct — the order card's stage due date, not Friday. "Arun to confirm the advance before production starts" got no due date at all.</t>
+        </is>
+      </c>
+      <c r="F50" s="26" t="inlineStr">
+        <is>
+          <t>Use the date the person said; when none, say "no date - set one" in the review instead of saving without one.</t>
+        </is>
+      </c>
+      <c r="G50" s="26" t="inlineStr">
+        <is>
+          <t>4. Fix the bugs found (P1)</t>
+        </is>
+      </c>
+      <c r="H50" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I50" s="26" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>C-14</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C51" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D51" s="26" t="inlineStr">
+        <is>
+          <t>Decisions → duplicates</t>
+        </is>
+      </c>
+      <c r="E51" s="26" t="inlineStr">
+        <is>
+          <t>The order card already had "Raise the pro-forma invoice…" and "Verify advance payment or LC…" (on the Accounts team). Dex created "Send revised pro-forma invoice" (Rahul) and "Confirm 30% advance payment received" (Arun) beside them — the order now carries both pairs.</t>
+        </is>
+      </c>
+      <c r="F51" s="26" t="inlineStr">
+        <is>
+          <t>When a decision names work the card already has, assign/re-date that task instead of adding a twin.</t>
+        </is>
+      </c>
+      <c r="G51" s="26" t="inlineStr">
+        <is>
+          <t>5. Getting a team in (P1/P2)</t>
+        </is>
+      </c>
+      <c r="H51" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I51" s="26" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>C-15</t>
+        </is>
+      </c>
+      <c r="B52" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C52" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D52" s="26" t="inlineStr">
+        <is>
+          <t>Decisions → after Approve</t>
+        </is>
+      </c>
+      <c r="E52" s="26" t="inlineStr">
+        <is>
+          <t>"Approved — 2 tasks created" toast after ~10 s, but the dialog stayed open showing the pre-approval "Decision ready for you" screen (buttons gone). It looks like nothing happened.</t>
+        </is>
+      </c>
+      <c r="F52" s="26" t="inlineStr">
+        <is>
+          <t>Close, or switch to "Approved - here's what was created" with links.</t>
+        </is>
+      </c>
+      <c r="G52" s="26" t="inlineStr">
+        <is>
+          <t>8. Speed and feedback (P2)</t>
+        </is>
+      </c>
+      <c r="H52" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I52" s="26" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>C-16</t>
+        </is>
+      </c>
+      <c r="B53" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C53" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D53" s="26" t="inlineStr">
+        <is>
+          <t>Decisions review</t>
+        </is>
+      </c>
+      <c r="E53" s="26" t="inlineStr">
+        <is>
+          <t>The company-note line shows a raw tag "buyer_terms".</t>
+        </is>
+      </c>
+      <c r="F53" s="26" t="inlineStr">
+        <is>
+          <t>Show the note's words only, or a friendly label.</t>
+        </is>
+      </c>
+      <c r="G53" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H53" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I53" s="26" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="24" t="inlineStr">
+        <is>
+          <t>C-17</t>
+        </is>
+      </c>
+      <c r="B54" s="29" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="C54" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D54" s="26" t="inlineStr">
+        <is>
+          <t>Decisions (Dex)</t>
+        </is>
+      </c>
+      <c r="E54" s="26" t="inlineStr">
+        <is>
+          <t>The decision flow is the product at its best: one typed sentence → recognised Rahul and Arun, linked the existing NW-001 card, proposed tasks + a company note, and nothing was created until Approve. The progress dialog ("Sending… Queued… Working out who does what") can be closed while it works.</t>
+        </is>
+      </c>
+      <c r="F54" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" s="26" t="inlineStr">
+        <is>
+          <t>Works - no action</t>
+        </is>
+      </c>
+      <c r="I54" s="26" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="24" t="inlineStr">
+        <is>
+          <t>C-18</t>
+        </is>
+      </c>
+      <c r="B55" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D55" s="26" t="inlineStr">
+        <is>
+          <t>My Work → routines</t>
+        </is>
+      </c>
+      <c r="E55" s="26" t="inlineStr">
+        <is>
+          <t>"Set them up" starts routines with a frequency but no "who": all three were assigned to the owner, including "Monthly export invoice reconciliation with Accounts". Took ~8 s with no busy state.</t>
+        </is>
+      </c>
+      <c r="F55" s="26" t="inlineStr">
+        <is>
+          <t>Pick an assignee (or team) per routine, defaulting from its department.</t>
+        </is>
+      </c>
+      <c r="G55" s="26" t="inlineStr">
+        <is>
+          <t>5. Getting a team in (P1/P2)</t>
+        </is>
+      </c>
+      <c r="H55" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I55" s="26" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="24" t="inlineStr">
+        <is>
+          <t>C-19</t>
+        </is>
+      </c>
+      <c r="B56" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C56" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D56" s="26" t="inlineStr">
+        <is>
+          <t>My Work → new task</t>
+        </is>
+      </c>
+      <c r="E56" s="26" t="inlineStr">
+        <is>
+          <t>Assigning to someone whose invite is still pending gives no hint they cannot see it yet. An empty title is only a red outline (no words).</t>
+        </is>
+      </c>
+      <c r="F56" s="26" t="inlineStr">
+        <is>
+          <t>"Rahul hasn't joined yet - they'll see it once they do." / "Give the task a title."</t>
+        </is>
+      </c>
+      <c r="G56" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H56" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I56" s="26" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
+          <t>C-20</t>
+        </is>
+      </c>
+      <c r="B57" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="inlineStr">
+        <is>
+          <t>Team / CRM / Workflows / My Work / Decisions</t>
+        </is>
+      </c>
+      <c r="D57" s="26" t="inlineStr">
+        <is>
+          <t>My Work → new task "Department"</t>
+        </is>
+      </c>
+      <c r="E57" s="26" t="inlineStr">
+        <is>
+          <t>The task form's Department list is the task categories (Buyer Coordination…), not the teams — B-02 seen in daily use.</t>
+        </is>
+      </c>
+      <c r="F57" s="26" t="inlineStr">
+        <is>
+          <t>One list (see B-02).</t>
+        </is>
+      </c>
+      <c r="G57" s="26" t="inlineStr">
+        <is>
+          <t>3. Make the setup match what the founder said (P1)</t>
+        </is>
+      </c>
+      <c r="H57" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I57" s="26" t="inlineStr">
+        <is>
+          <t>FIXED with B-02: the New Task Department list is the teams (verified live: 7 teams).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="24" t="inlineStr">
+        <is>
+          <t>F-01</t>
+        </is>
+      </c>
+      <c r="B58" s="30" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D58" s="26" t="inlineStr">
+        <is>
+          <t>Finance → Ask AI about your finances</t>
+        </is>
+      </c>
+      <c r="E58" s="26" t="inlineStr">
+        <is>
+          <t>Asked "How much do we owe suppliers and when is it due?" The answer: "there are no outstanding payables… ₹0… [the yarn] appears to already be fully paid for." A ₹1,68,000 purchase bill from Sri Lakshmi Yarn Mills is stored unpaid, due 5 Nov (checked via the API). Purchase bills booked as stock are left out of what the AI is given. A confident wrong answer about money.</t>
+        </is>
+      </c>
+      <c r="F58" s="26" t="inlineStr">
+        <is>
+          <t>Payables (all unpaid purchase bills, whatever they were booked as) in the finance context; tests for "what do we owe".</t>
+        </is>
+      </c>
+      <c r="G58" s="26" t="inlineStr">
+        <is>
+          <t>1. Money answers must be right (P0)</t>
+        </is>
+      </c>
+      <c r="H58" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I58" s="26" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="24" t="inlineStr">
+        <is>
+          <t>F-02</t>
+        </is>
+      </c>
+      <c r="B59" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D59" s="26" t="inlineStr">
+        <is>
+          <t>Finance → record a payment</t>
+        </is>
+      </c>
+      <c r="E59" s="26" t="inlineStr">
+        <is>
+          <t>An invoice row's only action is "Delete invoice"; "Add record" offers Income / Expense / Asset / Inventory — no "Payment received" or "Mark paid / part-paid". Payments only arrive via WhatsApp or an uploaded receipt. An owner who got a bank transfer cannot record it.</t>
+        </is>
+      </c>
+      <c r="F59" s="26" t="inlineStr">
+        <is>
+          <t>"Record payment" on each invoice and bill (amount, date, mode), part-payments, and a payment record type.</t>
+        </is>
+      </c>
+      <c r="G59" s="26" t="inlineStr">
+        <is>
+          <t>2. Close the money loop (P1)</t>
+        </is>
+      </c>
+      <c r="H59" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I59" s="26" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="B60" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D60" s="26" t="inlineStr">
+        <is>
+          <t>Finance → sales invoice</t>
+        </is>
+      </c>
+      <c r="E60" s="26" t="inlineStr">
+        <is>
+          <t>"Income" records a sale (what for, amount, buyer, number, dates) but cannot produce an invoice: no line items, GST, HSN, bank details or PDF to send; no currency for an export sale (GBP/USD) — amounts are ₹ only.</t>
+        </is>
+      </c>
+      <c r="F60" s="26" t="inlineStr">
+        <is>
+          <t>Generate a GST invoice / export invoice (line items, tax, currency, PDF); at minimum a currency per invoice.</t>
+        </is>
+      </c>
+      <c r="G60" s="26" t="inlineStr">
+        <is>
+          <t>2. Close the money loop (P1)</t>
+        </is>
+      </c>
+      <c r="H60" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I60" s="26" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="24" t="inlineStr">
+        <is>
+          <t>F-04</t>
+        </is>
+      </c>
+      <c r="B61" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D61" s="26" t="inlineStr">
+        <is>
+          <t>Finance → Overview "Net profit" and payables</t>
+        </is>
+      </c>
+      <c r="E61" s="26" t="inlineStr">
+        <is>
+          <t>Net profit shows ₹11,50,000 = the whole sale, though ₹1,68,000 of yarn went into it (stock bought, cost never reaches profit). No "to pay" figure anywhere on Overview; the ₹1,68,000 owed is invisible unless you open the bill list. The AI brief itself says "P&amp;L looks artificially perfect".</t>
+        </is>
+      </c>
+      <c r="F61" s="26" t="inlineStr">
+        <is>
+          <t>A "To pay" tile beside "To collect"; profit that counts stock used (or label it "before cost of goods").</t>
+        </is>
+      </c>
+      <c r="G61" s="26" t="inlineStr">
+        <is>
+          <t>2. Close the money loop (P1)</t>
+        </is>
+      </c>
+      <c r="H61" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I61" s="26" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="24" t="inlineStr">
+        <is>
+          <t>F-05</t>
+        </is>
+      </c>
+      <c r="B62" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C62" s="26" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D62" s="26" t="inlineStr">
+        <is>
+          <t>Bill reading → GST</t>
+        </is>
+      </c>
+      <c r="E62" s="26" t="inlineStr">
+        <is>
+          <t>The bill showed the supplier's GSTIN and CGST 2.5% + SGST 2.5%; neither was captured (contact GSTIN stays empty; no tax split). Stock unit cost was set to ₹336/kg = price including GST, which is normally claimable input credit.</t>
+        </is>
+      </c>
+      <c r="F62" s="26" t="inlineStr">
+        <is>
+          <t>Read GSTIN and the tax split; keep GST out of stock cost and track input credit.</t>
+        </is>
+      </c>
+      <c r="G62" s="26" t="inlineStr">
+        <is>
+          <t>2. Close the money loop (P1)</t>
+        </is>
+      </c>
+      <c r="H62" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I62" s="26" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>F-06</t>
+        </is>
+      </c>
+      <c r="B63" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D63" s="26" t="inlineStr">
+        <is>
+          <t>Finance overview</t>
+        </is>
+      </c>
+      <c r="E63" s="26" t="inlineStr">
+        <is>
+          <t>The AI Finance Brief ran on a brand-new company with no data ("No financial data found… Zero records across all financial categories") — AI allowance spent to say nothing. Two "Ask about your finances" boxes on the same page. Amounts carry hidden zero-width characters (copying "₹11,50,000" into a sheet brings them along). "Filed: 0 contacts · 1 invoices · 0 payments · 1 tasks" (plurals).</t>
+        </is>
+      </c>
+      <c r="F63" s="26" t="inlineStr">
+        <is>
+          <t>Skip the brief until there is data; one ask box; plain digits; "1 bill · 1 task".</t>
+        </is>
+      </c>
+      <c r="G63" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H63" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I63" s="26" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="24" t="inlineStr">
+        <is>
+          <t>F-07</t>
+        </is>
+      </c>
+      <c r="B64" s="29" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="D64" s="26" t="inlineStr">
+        <is>
+          <t>Bill reading</t>
+        </is>
+      </c>
+      <c r="E64" s="26" t="inlineStr">
+        <is>
+          <t>Good: a supplier tax invoice (image) was read in ~28 s at 98% confidence — supplier, number, ₹1,68,000, due date, "book as Inventory", a "Pay vendor bill" task; it matched the existing supplier instead of duplicating; stock got 500 kg. The brief rewrote itself from the real figures after the books changed.</t>
+        </is>
+      </c>
+      <c r="F64" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" s="26" t="inlineStr">
+        <is>
+          <t>Works - no action</t>
+        </is>
+      </c>
+      <c r="I64" s="26" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="24" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="B65" s="30" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="C65" s="26" t="inlineStr">
+        <is>
+          <t>Dex / Brain / other pages</t>
+        </is>
+      </c>
+      <c r="D65" s="26" t="inlineStr">
+        <is>
+          <t>Dex → "What do we owe suppliers, and when is it due?"</t>
+        </is>
+      </c>
+      <c r="E65" s="26" t="inlineStr">
+        <is>
+          <t>Dex listed the supplier bill correctly (₹1,68,000, due 5 Nov) and Northwind's sales invoice (money owed *to* us) as a "supplier/vendor invoice", answering "2 outstanding supplier invoices totalling Rs 13,18,000". The truth is ₹1,68,000. Together with F-01, the two money AIs give two different wrong answers to the same question.</t>
+        </is>
+      </c>
+      <c r="F65" s="26" t="inlineStr">
+        <is>
+          <t>When the question is about suppliers/payables, only purchase bills; when about buyers/receivables, only sales invoices. Add both to the eval golden set.</t>
+        </is>
+      </c>
+      <c r="G65" s="26" t="inlineStr">
+        <is>
+          <t>1. Money answers must be right (P0)</t>
+        </is>
+      </c>
+      <c r="H65" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I65" s="26" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="B66" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C66" s="26" t="inlineStr">
+        <is>
+          <t>Dex / Brain / other pages</t>
+        </is>
+      </c>
+      <c r="D66" s="26" t="inlineStr">
+        <is>
+          <t>Ops (operating score)</t>
+        </is>
+      </c>
+      <c r="E66" s="26" t="inlineStr">
+        <is>
+          <t>Day one: "Finance 0/100" because no cash has come in yet (a new company is penalised for being new); "Sales 100/100" is described as "Rate at which raised decisions get a green light" — that is approvals, not sales. "Do these first: Nothing urgent" while the score says "Some key areas need attention".</t>
+        </is>
+      </c>
+      <c r="F66" s="26" t="inlineStr">
+        <is>
+          <t>Don't score an area with nothing to measure ("not enough yet"); rename Sales; when the score is low, say what to do first.</t>
+        </is>
+      </c>
+      <c r="G66" s="26" t="inlineStr">
+        <is>
+          <t>9. Smaller product gaps (P2)</t>
+        </is>
+      </c>
+      <c r="H66" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I66" s="26" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="24" t="inlineStr">
+        <is>
+          <t>G-03</t>
+        </is>
+      </c>
+      <c r="B67" s="29" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="C67" s="26" t="inlineStr">
+        <is>
+          <t>Dex / Brain / other pages</t>
+        </is>
+      </c>
+      <c r="D67" s="26" t="inlineStr">
+        <is>
+          <t>Dex / Brain / Journal</t>
+        </is>
+      </c>
+      <c r="E67" s="26" t="inlineStr">
+        <is>
+          <t>Good: "Where is NW-001 and what is pending?" — right stage, both pending tasks from the decision, the discount note, 5 linked sources. A leave policy uploaded to the Company Brain answered "how many sick days / when is a certificate needed" correctly with the document cited and three good follow-ups. The Journal shows the decision with a timeline. Notifications already carried a due-tomorrow reminder.</t>
+        </is>
+      </c>
+      <c r="F67" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H67" s="26" t="inlineStr">
+        <is>
+          <t>Works - no action</t>
+        </is>
+      </c>
+      <c r="I67" s="26" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="24" t="inlineStr">
+        <is>
+          <t>G-04</t>
+        </is>
+      </c>
+      <c r="B68" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C68" s="26" t="inlineStr">
+        <is>
+          <t>Dex / Brain / other pages</t>
+        </is>
+      </c>
+      <c r="D68" s="26" t="inlineStr">
+        <is>
+          <t>Leave vs Company Brain</t>
+        </is>
+      </c>
+      <c r="E68" s="26" t="inlineStr">
+        <is>
+          <t>The leave policy (12 casual / 8 sick / 15 earned, carry-forward) lives only as a document Dex can quote. The Leave form has types (Casual, Sick, Earned, Permission, WFH, Other) but no allowances or balances ("Days off in 2026: 1"), so nobody can see how many days they have left and approvers can't see if someone is over.</t>
+        </is>
+      </c>
+      <c r="F68" s="26" t="inlineStr">
+        <is>
+          <t>Allowance per type (Settings) and a balance on Leave and on the approval card.</t>
+        </is>
+      </c>
+      <c r="G68" s="26" t="inlineStr">
+        <is>
+          <t>9. Smaller product gaps (P2)</t>
+        </is>
+      </c>
+      <c r="H68" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I68" s="26" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="24" t="inlineStr">
+        <is>
+          <t>D-01</t>
+        </is>
+      </c>
+      <c r="B69" s="25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C69" s="26" t="inlineStr">
+        <is>
+          <t>Signed in as each role</t>
+        </is>
+      </c>
+      <c r="D69" s="26" t="inlineStr">
+        <is>
+          <t>HR (Kavitha) → Settings → Workspace tab</t>
+        </is>
+      </c>
+      <c r="E69" s="26" t="inlineStr">
+        <is>
+          <t>Opening /settings?tab=workspace as a member crashes the panel: "Something broke here — Maximum update depth exceeded" (a render loop). Reproduced on a fresh load. After it, every other Settings tab shows the same crash until a full reload.</t>
+        </is>
+      </c>
+      <c r="F69" s="26" t="inlineStr">
+        <is>
+          <t>A member asking for an owner-only tab lands on their own Account tab.</t>
+        </is>
+      </c>
+      <c r="G69" s="26" t="inlineStr">
+        <is>
+          <t>4. Fix the bugs found (P1)</t>
+        </is>
+      </c>
+      <c r="H69" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I69" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push). Settings.js tabAllowed(): the URL can only pick a tab the person can open; the sync effect and the owner guard no longer ping-pong. Live as Kavitha (HR): /settings?tab=workspace renders her Account view, no error, no console errors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="24" t="inlineStr">
+        <is>
+          <t>D-02</t>
+        </is>
+      </c>
+      <c r="B70" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C70" s="26" t="inlineStr">
+        <is>
+          <t>Signed in as each role</t>
+        </is>
+      </c>
+      <c r="D70" s="26" t="inlineStr">
+        <is>
+          <t>Every member → Dex box on the Desk</t>
+        </is>
+      </c>
+      <c r="E70" s="26" t="inlineStr">
+        <is>
+          <t>HR and Sales both see "Dex — Ask an owner to turn on capture": Voice Box is off by default for every team, so the product's main action (tell Dex a decision) is unavailable to the whole team until the owner finds the switch.</t>
+        </is>
+      </c>
+      <c r="F70" s="26" t="inlineStr">
+        <is>
+          <t>Capture on by default for team members (decisions still need approval), or prompt the owner during setup.</t>
+        </is>
+      </c>
+      <c r="G70" s="26" t="inlineStr">
+        <is>
+          <t>5. Getting a team in (P1/P2)</t>
+        </is>
+      </c>
+      <c r="H70" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I70" s="26" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="24" t="inlineStr">
+        <is>
+          <t>D-03</t>
+        </is>
+      </c>
+      <c r="B71" s="27" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C71" s="26" t="inlineStr">
+        <is>
+          <t>Signed in as each role</t>
+        </is>
+      </c>
+      <c r="D71" s="26" t="inlineStr">
+        <is>
+          <t>Invite link → privacy</t>
+        </is>
+      </c>
+      <c r="E71" s="26" t="inlineStr">
+        <is>
+          <t>The invite page masks the number ("•••• 0002"), but the invite's start response returns the full phone number and name to anyone holding the link (the link is meant to be shared over WhatsApp).</t>
+        </is>
+      </c>
+      <c r="F71" s="26" t="inlineStr">
+        <is>
+          <t>Return only the masked number.</t>
+        </is>
+      </c>
+      <c r="G71" s="26" t="inlineStr">
+        <is>
+          <t>7. Trust and privacy (P2)</t>
+        </is>
+      </c>
+      <c r="H71" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I71" s="26" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="24" t="inlineStr">
+        <is>
+          <t>D-04</t>
+        </is>
+      </c>
+      <c r="B72" s="28" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C72" s="26" t="inlineStr">
+        <is>
+          <t>Signed in as each role</t>
+        </is>
+      </c>
+      <c r="D72" s="26" t="inlineStr">
+        <is>
+          <t>Leave request (Sales)</t>
+        </is>
+      </c>
+      <c r="E72" s="26" t="inlineStr">
+        <is>
+          <t>Rahul's request went to "Approver: Meera Iyer" (owner) because every team's leave approver is the owner by default (see B-01); dates show as "2026-10-15 → 2026-10-16".</t>
+        </is>
+      </c>
+      <c r="F72" s="26" t="inlineStr">
+        <is>
+          <t>Readable dates ("15–16 Oct"); approvers from setup.</t>
+        </is>
+      </c>
+      <c r="G72" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H72" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I72" s="26" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="24" t="inlineStr">
+        <is>
+          <t>D-05</t>
+        </is>
+      </c>
+      <c r="B73" s="29" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="C73" s="26" t="inlineStr">
+        <is>
+          <t>Signed in as each role</t>
+        </is>
+      </c>
+      <c r="D73" s="26" t="inlineStr">
+        <is>
+          <t>Access control</t>
+        </is>
+      </c>
+      <c r="E73" s="26" t="inlineStr">
+        <is>
+          <t>Holds up well. HR: CRM and Journal show "This page isn't open to you"; Finance shows the upload inbox only; Team is a clearly labelled read-only view; the API refuses invoices/contacts/expenses/ledger with 403. Sales: Dex refuses money ("invoices, payments and balances aren't part of your access") and still answers what Sales can see. Accounts sees all of Finance. Members get their own welcome ("check the details your team added"). Proof-required tasks cannot be completed without a file.</t>
+        </is>
+      </c>
+      <c r="F73" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" s="26" t="inlineStr">
+        <is>
+          <t>Works - no action</t>
+        </is>
+      </c>
+      <c r="I73" s="26" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="24" t="inlineStr">
+        <is>
+          <t>D-06</t>
+        </is>
+      </c>
+      <c r="B74" s="29" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="C74" s="26" t="inlineStr">
+        <is>
+          <t>Signed in as each role</t>
+        </is>
+      </c>
+      <c r="D74" s="26" t="inlineStr">
+        <is>
+          <t>Phone width (375 px)</t>
+        </is>
+      </c>
+      <c r="E74" s="26" t="inlineStr">
+        <is>
+          <t>Desk, My Work, Finance, CRM, Team and Settings have no sideways scroll.</t>
+        </is>
+      </c>
+      <c r="F74" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" s="26" t="inlineStr">
+        <is>
+          <t>Works - no action</t>
+        </is>
+      </c>
+      <c r="I74" s="26" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:I74"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1650,7 +1650,7 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>70 findings (58 to act on) in the "Product Audit 2026-10-08" sheet. Batch 1 done 2026-10-08: B-02 + C-20 one department list (the teams), D-01 Settings crash for members, A-01 sign-up resume, B-04 + C-01 plan card (trial, upgrade, AI allowance, one seat count), A-16 bring your team in.</t>
+          <t>70 findings (58 to act on) in the "Product Audit 2026-10-08" sheet. Batch 1 done 2026-10-08: B-02 + C-20 one department list (the teams), D-01 Settings crash for members, A-01 sign-up resume, B-04 + C-01 plan card (trial, upgrade, AI allowance, one seat count), A-16 bring your team in. Batch 2 done 2026-10-08: F-02 record payments + bills to pay, F-03 GST/export invoices + PDF, F-04 To collect/To pay + profit after stock used, B-01 interview approval rules become settings (F-01, B-03 partly).</t>
         </is>
       </c>
     </row>
@@ -12907,10 +12907,14 @@
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I25" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I25" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push). New AI step generators.approval_rules (prompt v1.1 + eval case) maps the interview's free-text rules onto real team/stage keys after the operating model exists; validated, then applied: stage_limit -&gt; pipeline.approval_delegate {role, up_to} (engine lets that team move a card into the sign-off stage within the limit; above it / no value -&gt; owner, with the reason), leave_approver -&gt; tenant.leave_approver_teams (resolved to an active member of that team with leave_approve), money_threshold -&gt; high_value_threshold + require_owner_signoff; anything else is a note. Runs after sign-up's background setup; Settings &gt; Operations "Approvals from your sign-up" lists each rule and what it became, with Apply again; the operating-model editor shows/edits the delegate; leave approvers show "HR team (from your sign-up)". Live on Audit Textiles: Sales confirms up to 5,00,000 (3L order advanced by Rahul, 7L refused "Above 5,00,000 the owner approves"), Rahul's leave -&gt; Kavitha, threshold 1,00,000; discount %, rework, peak-season leave, QC-before-freight kept as notes.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -12997,10 +13001,14 @@
       </c>
       <c r="H27" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I27" s="26" t="inlineStr"/>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="I27" s="26" t="inlineStr">
+        <is>
+          <t>PARTLY FIXED with B-01: value-based sign-off stage (approval_delegate) now exists and is editable in Settings &gt; Operations. Per-stage gate conditions beyond the sign-off stage still open.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="24" t="inlineStr">
@@ -14342,10 +14350,14 @@
       </c>
       <c r="H58" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I58" s="26" t="inlineStr"/>
+          <t>Partly fixed</t>
+        </is>
+      </c>
+      <c r="I58" s="26" t="inlineStr">
+        <is>
+          <t>PARTLY FIXED 2026-10-08 (with F-04): the Finance AI context now carries payables_outstanding and payables_due (every unpaid purchase bill incl. those booked as stock). G-01 (Dex mixing receivables into "what we owe") still open.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="24" t="inlineStr">
@@ -14385,10 +14397,14 @@
       </c>
       <c r="H59" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I59" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I59" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push). POST /invoices/{id}/payments (routers/invoicing.py): money received on a sales invoice or paid on a supplier bill, full or part, method + reference; reuses the ledger's compare-and-set allocation (no double-pay); a bill paid in full marks its expense paid. UI: "Record payment" on each invoice row; new "Bills to pay" list on Expenses (purchase bills had no list anywhere). Live: Northwind 3,45,000 part payment -&gt; "Partial, bal 8,05,000"; yarn bill paid in full by UPI -&gt; gone from Bills to pay, To pay 0.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="24" t="inlineStr">
@@ -14428,10 +14444,14 @@
       </c>
       <c r="H60" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I60" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I60" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push). Finance &gt; Add record &gt; Invoice: GST invoice builder (line items, HSN/SAC, qty, unit, rate, GST %), CGST+SGST inside the seller's state, IGST across states, export in GBP/USD/EUR/AED/SGD with no GST (LUT), rounded to the rupee, number series PREFIX/FY/NNN continuing after hand-typed ones, GSTIN format check. GET /invoices/{id}/pdf (reportlab A4 tax/export invoice: header, buyer, items, tax lines, amount in words, bank details, terms, signatory); PDF button on every invoice row. Settings &gt; Company details gained "On your invoices" (address, state, bank, IFSC, UPI, prefix, terms). Live: AT/26-27/002 Karnataka -&gt; IGST 2,400, total 50,400; AT/26-27/003 export GBP 160; both PDFs checked. KNOWN GAP: Revenue totals add a foreign-currency invoice at face value (no exchange rate) -- same as before for Income in other currencies.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="24" t="inlineStr">
@@ -14471,10 +14491,14 @@
       </c>
       <c r="H61" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I61" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I61" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push). Overview: "To collect" and "To pay" tiles (8 tiles, 4x2). Profit: J2-06 kept (stock BOUGHT is not a loss); stock USED is the cost of goods sold -- Inventory &gt; Use (POST /inventory/{id}/use, stock_movements, CAS on quantity) and net profit = billed - operating spend - stock used; the tile says "after X of stock used", or "stock used isn't recorded yet" when there is stock and sales but no usage. Live: use 500 kg yarn -&gt; net profit 11,50,000 -&gt; 9,82,000.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="24" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -1170,7 +1170,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1650,7 +1649,7 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1660,7 +1659,7 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -1670,7 +1669,7 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>70 findings (58 to act on) in the "Product Audit 2026-10-08" sheet. Batch 1 done 2026-10-08: B-02 + C-20 one department list (the teams), D-01 Settings crash for members, A-01 sign-up resume, B-04 + C-01 plan card (trial, upgrade, AI allowance, one seat count), A-16 bring your team in. Batch 2 done 2026-10-08: F-02 record payments + bills to pay, F-03 GST/export invoices + PDF, F-04 To collect/To pay + profit after stock used, B-01 interview approval rules become settings (F-01, B-03 partly).</t>
+          <t>70 findings (58 to act on) in the "Product Audit 2026-10-08" sheet. Batch 1 done 2026-10-08: B-02 + C-20 one department list (the teams), D-01 Settings crash for members, A-01 sign-up resume, B-04 + C-01 plan card (trial, upgrade, AI allowance, one seat count), A-16 bring your team in. Batch 2 done 2026-10-08: F-02 record payments + bills to pay, F-03 GST/export invoices + PDF, F-04 To collect/To pay + profit after stock used, B-01 interview approval rules become settings (F-01, B-03 partly). Then: A-11 approval rules on the sign-up review; foreign-currency invoices counted at their exchange rate.</t>
         </is>
       </c>
     </row>
@@ -12473,10 +12472,14 @@
       </c>
       <c r="H15" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I15" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push). The sign-up review shows "Who signs off - from your answers": each interview approval rule in the founder's words, what happens to it (becomes a setting where the app has one, else a note, editable in Settings &gt; Operations), and an X to leave one out (saved to the draft and to what register receives). "Tell Dex" still adds/corrects rules. Live: a resumed draft showed 3 rules; removing one survived a reload. ORDER FLOW DONE 2026-10-08 (awaiting push): the review also shows "How work moves" - the pipelines designed from the interview (POST /signup/interview/flow: operating model from the founder's answers + their rules laid on, cached per plan), drawn as a route (components/workflow/PipelineFlow: stations with owning team and work count, gold sign-off step with the rule in words, the open step's work below; across on desktop, a timeline on a phone). Register takes exactly that model and those rule actions (re-validated; no second AI design). The same route is in Settings &gt; Operations ("How work moves"). Live: a textile interview gave Sample Development &gt; Sample Approval &gt; Order Confirmation (Sales up to 5 lakh, above that you) &gt; Production &gt; Quality Inspection &gt; Shipment, plus Procurement and Buyer Development; phone timeline checked. HARDENED 2026-10-08: the design now runs in the BACKGROUND from the moment the plan exists (interview_blueprint/refine start it; state on the session: designing | ready | failed, stale after 180 s) and the review polls every 3 s with short requests - no request is held open past the ~60 s production proxy limit; only starting a design passes the AI rate gate. The route reads across only when every step gets 112 px (measured on the card, ResizeObserver), else it is a timeline - no step ever cut off, at any width or step count; team names wrap instead of truncating. Live: a fresh design took ~48 s (the first Anthropic key is out of credit; calls fall back to the second key) and arrived via polling.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
@@ -14449,7 +14452,7 @@
       </c>
       <c r="I60" s="26" t="inlineStr">
         <is>
-          <t>FIXED 2026-10-08 (awaiting push). Finance &gt; Add record &gt; Invoice: GST invoice builder (line items, HSN/SAC, qty, unit, rate, GST %), CGST+SGST inside the seller's state, IGST across states, export in GBP/USD/EUR/AED/SGD with no GST (LUT), rounded to the rupee, number series PREFIX/FY/NNN continuing after hand-typed ones, GSTIN format check. GET /invoices/{id}/pdf (reportlab A4 tax/export invoice: header, buyer, items, tax lines, amount in words, bank details, terms, signatory); PDF button on every invoice row. Settings &gt; Company details gained "On your invoices" (address, state, bank, IFSC, UPI, prefix, terms). Live: AT/26-27/002 Karnataka -&gt; IGST 2,400, total 50,400; AT/26-27/003 export GBP 160; both PDFs checked. KNOWN GAP: Revenue totals add a foreign-currency invoice at face value (no exchange rate) -- same as before for Income in other currencies.</t>
+          <t>FIXED 2026-10-08 (awaiting push). Finance &gt; Add record &gt; Invoice: GST invoice builder (line items, HSN/SAC, qty, unit, rate, GST %), CGST+SGST inside the seller's state, IGST across states, export in GBP/USD/EUR/AED/SGD with no GST (LUT), rounded to the rupee, number series PREFIX/FY/NNN continuing after hand-typed ones, GSTIN format check. GET /invoices/{id}/pdf (reportlab A4 tax/export invoice: header, buyer, items, tax lines, amount in words, bank details, terms, signatory); PDF button on every invoice row. Settings &gt; Company details gained "On your invoices" (address, state, bank, IFSC, UPI, prefix, terms). Live: AT/26-27/002 Karnataka -&gt; IGST 2,400, total 50,400; AT/26-27/003 export GBP 160; both PDFs checked. FX FIXED 2026-10-08 (awaiting push): a foreign invoice carries fx_rate (company currency per unit); every total (Finance summary, Revenue, Payables, Finance AI, Desk overdue, Dex invoice figures, contact profile, CRM pills) counts it in the company's currency (shared/money.py); one with no rate is left out and listed (needs_rate) with a 'Set rate' action - never counted at face value. The builder asks for the rate on an export (pre-filled with the last one used); payments take the invoice's rate. Live: GBP 160 left out (Billed 12,00,400) -&gt; rate 107.5 -&gt; counted as 17,200 (Billed 12,17,600). EXPENSES FX DONE 2026-10-08 (awaiting push): expenses carry fx_rate too; Spend, profit, categories, vendors and the Finance AI count them in rupees; no rate = left out + listed, "Set rate" on the expense row (PATCH /expenses/{id}/fx-rate); a bill's rate reaches the expense booked from it. Live: a USD 200 lab-test bill was left out (Spend 0) -&gt; rate 84 -&gt; Spend 16,800.</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Audit 2026-10-08" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Product Audit 2026-10-08'!$A$4:$I$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Product Audit 2026-10-08'!$A$4:$I$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -11918,7 +11918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -11949,7 +11949,7 @@
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
         <is>
-          <t>Tally: P0 2 / P1 11 / P2 29 / P3 16 / Info 12 = 70 findings</t>
+          <t>Tally: P0 3 / P1 15 / P2 39 / P3 20 / Info 14 = 91 findings</t>
         </is>
       </c>
     </row>
@@ -12313,7 +12313,7 @@
       </c>
       <c r="B12" s="28" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="C12" s="26" t="inlineStr">
@@ -12343,10 +12343,14 @@
       </c>
       <c r="H12" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I12" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="inlineStr">
+        <is>
+          <t>CONFIRMED + FIXED 2026-10-08 (awaiting push) - it was real, not automation: (a) the sign-in page auto-submitted on the 6th digit with the code from React state, one digit behind, so EVERY hand-typed code was refused "Incorrect OTP" (only the dev auto-fill, which uses the button, got in); (b) OtpBoxes rebuilt the code from a render-time copy and squeezed out gaps, losing digits typed quickly. Now submits the code as typed; the boxes keep 6 cells in a ref. Live: typed code refused before, signs in after (sign-in, multi-company picker, and the sign-up code step).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
@@ -15066,8 +15070,991 @@
       </c>
       <c r="I74" s="26" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" s="24" t="inlineStr">
+        <is>
+          <t>A-21</t>
+        </is>
+      </c>
+      <c r="B75" s="26" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C75" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D75" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up review, returning founder</t>
+        </is>
+      </c>
+      <c r="E75" s="26" t="inlineStr">
+        <is>
+          <t>A founder whose first "Enter" created the company (answer lost, or tab closed) came back to the saved sign-up: the review said "This email already has a workspace. Sign in instead" - its email pre-check stopped them before register, which would have signed them straight in.</t>
+        </is>
+      </c>
+      <c r="F75" s="26" t="inlineStr">
+        <is>
+          <t>Register decides; tell the founder it is theirs.</t>
+        </is>
+      </c>
+      <c r="G75" s="26" t="inlineStr">
+        <is>
+          <t>4. Fix the bugs found (P1)</t>
+        </is>
+      </c>
+      <c r="H75" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I75" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push): no pre-check before register (its same-mobile + same-company recovery signs them in); /signup/check-email with the confirmed-mobile proof answers yours=true, and the review says "You already created X - press the button to go in". Live: Lost Press Knits created behind the browser, the returning founder pressed Enter and landed in it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="24" t="inlineStr">
+        <is>
+          <t>A-22</t>
+        </is>
+      </c>
+      <c r="B76" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C76" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D76" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in after an unfinished sign-up</t>
+        </is>
+      </c>
+      <c r="E76" s="26" t="inlineStr">
+        <is>
+          <t>A sign-up left before the account existed: the number is "not registered" and the page offered "Start a new company with this number".</t>
+        </is>
+      </c>
+      <c r="F76" s="26" t="inlineStr">
+        <is>
+          <t>Offer to finish what they started.</t>
+        </is>
+      </c>
+      <c r="G76" s="26" t="inlineStr">
+        <is>
+          <t>4. Fix the bugs found (P1)</t>
+        </is>
+      </c>
+      <c r="H76" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I76" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push): with a sign-up saved in this browser the page says "You started signing up and didn't finish..." and the button is "Finish setting up your company" (resumes at the first unanswered step). "Sign in instead" on the review now carries the number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="24" t="inlineStr">
+        <is>
+          <t>A-23</t>
+        </is>
+      </c>
+      <c r="B77" s="26" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C77" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D77" s="26" t="inlineStr">
+        <is>
+          <t>Welcome screen across accounts</t>
+        </is>
+      </c>
+      <c r="E77" s="26" t="inlineStr">
+        <is>
+          <t>The one-time "Welcome, &lt;name&gt;" pane flag survived sign-out: the next person to sign in on the device got the previous founder's welcome, full-screen, over a Desk they could not click (it also covered the "Add people" card).</t>
+        </is>
+      </c>
+      <c r="F77" s="26" t="inlineStr">
+        <is>
+          <t>Clear it on sign-out.</t>
+        </is>
+      </c>
+      <c r="G77" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H77" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I77" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push): logout removes dos_welcome.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="24" t="inlineStr">
+        <is>
+          <t>A-24</t>
+        </is>
+      </c>
+      <c r="B78" s="26" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="C78" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D78" s="26" t="inlineStr">
+        <is>
+          <t>Team invite at the end of sign-up</t>
+        </is>
+      </c>
+      <c r="E78" s="26" t="inlineStr">
+        <is>
+          <t>Founder decision 2026-10-08: no "bring my team in first" at the end of sign-up - the founder goes straight in and invites from the Desk card / Team.</t>
+        </is>
+      </c>
+      <c r="F78" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" s="26" t="inlineStr">
+        <is>
+          <t>5. Getting a team in (P1/P2)</t>
+        </is>
+      </c>
+      <c r="H78" s="26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I78" s="26" t="inlineStr">
+        <is>
+          <t>Removed from BuildReveal; the Desk "Bring your team in" card stays (verified: Add people opens Add team member).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="24" t="inlineStr">
+        <is>
+          <t>A-25</t>
+        </is>
+      </c>
+      <c r="B79" s="26" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C79" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D79" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in, Email &amp; Password tab</t>
+        </is>
+      </c>
+      <c r="E79" s="26" t="inlineStr">
+        <is>
+          <t>An account that signed up by mobile has no password. Signing in with its email and any password crashed the server (KeyError password_hash, 500).</t>
+        </is>
+      </c>
+      <c r="F79" s="26" t="inlineStr">
+        <is>
+          <t>A normal "wrong password", and point them to the mobile code.</t>
+        </is>
+      </c>
+      <c r="G79" s="26" t="inlineStr">
+        <is>
+          <t>4. Fix the bugs found (P1)</t>
+        </is>
+      </c>
+      <c r="H79" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I79" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push): login treats a missing hash as a wrong password (same 401, lockout count and audit row); the tab shows "Signed up with your mobile number? ... sign in with a mobile code" under any refusal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="24" t="inlineStr">
+        <is>
+          <t>A-26</t>
+        </is>
+      </c>
+      <c r="B80" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C80" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D80" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in and sign-up code step</t>
+        </is>
+      </c>
+      <c r="E80" s="26" t="inlineStr">
+        <is>
+          <t>"Change", then the same number again inside 30 s: "Please wait 17s before requesting a new code" and the page stayed on the number, with nowhere to type the code that had already arrived.</t>
+        </is>
+      </c>
+      <c r="F80" s="26" t="inlineStr">
+        <is>
+          <t>Go to the code boxes and count down the resend.</t>
+        </is>
+      </c>
+      <c r="G80" s="26" t="inlineStr">
+        <is>
+          <t>4. Fix the bugs found (P1)</t>
+        </is>
+      </c>
+      <c r="H80" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I80" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push): a "please wait Ns" refusal opens the code step with the countdown, on Login.js and BasicsFlow.js.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="24" t="inlineStr">
+        <is>
+          <t>A-27</t>
+        </is>
+      </c>
+      <c r="B81" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C81" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D81" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in and sign-up code step</t>
+        </is>
+      </c>
+      <c r="E81" s="26" t="inlineStr">
+        <is>
+          <t>Five wrong codes spend the code ("Too many attempts", then "Request an OTP first"), but Resend stayed behind its 30 s countdown.</t>
+        </is>
+      </c>
+      <c r="F81" s="26" t="inlineStr">
+        <is>
+          <t>Say the code is spent and offer a new one now.</t>
+        </is>
+      </c>
+      <c r="G81" s="26" t="inlineStr">
+        <is>
+          <t>4. Fix the bugs found (P1)</t>
+        </is>
+      </c>
+      <c r="H81" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I81" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push): spent or expired code: "That code can't be used any more - send yourself a new one below." and Resend unlocks. Sign-up also puts the caret back in the first box after a wrong code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="24" t="inlineStr">
+        <is>
+          <t>A-28</t>
+        </is>
+      </c>
+      <c r="B82" s="26" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C82" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D82" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in, mobile number</t>
+        </is>
+      </c>
+      <c r="E82" s="26" t="inlineStr">
+        <is>
+          <t>0000000000 or a foreign number came back "No account" with "Start a new company with this number", and sign-up then refused the same number.</t>
+        </is>
+      </c>
+      <c r="F82" s="26" t="inlineStr">
+        <is>
+          <t>"Enter a 10-digit Indian mobile number".</t>
+        </is>
+      </c>
+      <c r="G82" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H82" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I82" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push): a 404 for a number that is not an Indian mobile shows the format message instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="24" t="inlineStr">
+        <is>
+          <t>A-29</t>
+        </is>
+      </c>
+      <c r="B83" s="26" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C83" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D83" s="26" t="inlineStr">
+        <is>
+          <t>Sign out on the Terms screen</t>
+        </is>
+      </c>
+      <c r="E83" s="26" t="inlineStr">
+        <is>
+          <t>Sign out on "Before you carry on" (and on the owner-credentials screen, and the demo banner's Leave) ended the session and left a blank page until a reload.</t>
+        </is>
+      </c>
+      <c r="F83" s="26" t="inlineStr">
+        <is>
+          <t>Go to the sign-in page, as every other Sign out does.</t>
+        </is>
+      </c>
+      <c r="G83" s="26" t="inlineStr">
+        <is>
+          <t>4. Fix the bugs found (P1)</t>
+        </is>
+      </c>
+      <c r="H83" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I83" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push): TermsGate, OwnerCredentialsGate and DemoWorkspaceBanner await logout and navigate to /login. Verified in the browser for the first and third.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="24" t="inlineStr">
+        <is>
+          <t>A-30</t>
+        </is>
+      </c>
+      <c r="B84" s="26" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C84" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D84" s="26" t="inlineStr">
+        <is>
+          <t>First screen after sign-up</t>
+        </is>
+      </c>
+      <c r="E84" s="26" t="inlineStr">
+        <is>
+          <t>A founder ticks the Terms at sign-up, enters, and the first thing inside is the Terms again ("Before you carry on"), over their welcome screen. The review built the register request field by field and left terms_version out, so the agreement was never recorded.</t>
+        </is>
+      </c>
+      <c r="F84" s="26" t="inlineStr">
+        <is>
+          <t>Record it at register.</t>
+        </is>
+      </c>
+      <c r="G84" s="26" t="inlineStr">
+        <is>
+          <t>4. Fix the bugs found (P1)</t>
+        </is>
+      </c>
+      <c r="H84" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I84" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push): BuildReveal sends terms_version. Verified: a fresh sign-up stores terms_accepted 2026-10-08 and no Terms screen appears.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="24" t="inlineStr">
+        <is>
+          <t>A-31</t>
+        </is>
+      </c>
+      <c r="B85" s="26" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C85" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D85" s="26" t="inlineStr">
+        <is>
+          <t>Register</t>
+        </is>
+      </c>
+      <c r="E85" s="26" t="inlineStr">
+        <is>
+          <t>Names were stored with the spaces typed around them ("  Signup Tester  ").</t>
+        </is>
+      </c>
+      <c r="F85" s="26" t="inlineStr">
+        <is>
+          <t>Trim.</t>
+        </is>
+      </c>
+      <c r="G85" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H85" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I85" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push): register strips company_name and name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="24" t="inlineStr">
+        <is>
+          <t>A-32</t>
+        </is>
+      </c>
+      <c r="B86" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C86" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D86" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up consent</t>
+        </is>
+      </c>
+      <c r="E86" s="26" t="inlineStr">
+        <is>
+          <t>The AI/Terms agreement lived in the browser tab, not the sign-up: after a sign-out, the next person to sign up in the same tab skipped the consent step and was recorded as agreeing.</t>
+        </is>
+      </c>
+      <c r="F86" s="26" t="inlineStr">
+        <is>
+          <t>The agreement ends with the sign-up.</t>
+        </is>
+      </c>
+      <c r="G86" s="26" t="inlineStr">
+        <is>
+          <t>7. Trust and privacy (P2)</t>
+        </is>
+      </c>
+      <c r="H86" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I86" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push): clearSignupConsent() on finishing sign-up and on sign-out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="24" t="inlineStr">
+        <is>
+          <t>A-33</t>
+        </is>
+      </c>
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C87" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D87" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up Back and resume</t>
+        </is>
+      </c>
+      <c r="E87" s="26" t="inlineStr">
+        <is>
+          <t>Back from the consent or website screen reopened the wizard at question one (mobile). A resumed sign-up with every basic answered reopened at question three (company), so every answer was walked again.</t>
+        </is>
+      </c>
+      <c r="F87" s="26" t="inlineStr">
+        <is>
+          <t>Land on the last question, team size.</t>
+        </is>
+      </c>
+      <c r="G87" s="26" t="inlineStr">
+        <is>
+          <t>9. Smaller product gaps (P2)</t>
+        </is>
+      </c>
+      <c r="H87" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I87" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push): backToBasics() and the resume fallback both open at team size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="24" t="inlineStr">
+        <is>
+          <t>A-34</t>
+        </is>
+      </c>
+      <c r="B88" s="26" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C88" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D88" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up interview language, website step</t>
+        </is>
+      </c>
+      <c r="E88" s="26" t="inlineStr">
+        <is>
+          <t>The interview's language screen had only "Skip", no Back. Coming back to the website step forgot the industry and website already given.</t>
+        </is>
+      </c>
+      <c r="F88" s="26" t="inlineStr">
+        <is>
+          <t>A Back; keep the answer.</t>
+        </is>
+      </c>
+      <c r="G88" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H88" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I88" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push): Back on the language screen; WebsiteIntel starts from the saved answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="24" t="inlineStr">
+        <is>
+          <t>A-35</t>
+        </is>
+      </c>
+      <c r="B89" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C89" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D89" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up review, recurring tasks</t>
+        </is>
+      </c>
+      <c r="E89" s="26" t="inlineStr">
+        <is>
+          <t>The review listed the first 8 recurring tasks. A task added with "Missing something? Tell Dex" lands ninth: the tile said 9 and the founder never saw their addition.</t>
+        </is>
+      </c>
+      <c r="F89" s="26" t="inlineStr">
+        <is>
+          <t>List them all.</t>
+        </is>
+      </c>
+      <c r="G89" s="26" t="inlineStr">
+        <is>
+          <t>9. Smaller product gaps (P2)</t>
+        </is>
+      </c>
+      <c r="H89" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I89" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push): no cap on the list. Verified: the Saturday maintenance task appears.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="24" t="inlineStr">
+        <is>
+          <t>A-36</t>
+        </is>
+      </c>
+      <c r="B90" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C90" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D90" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up, number that already owns a company</t>
+        </is>
+      </c>
+      <c r="E90" s="26" t="inlineStr">
+        <is>
+          <t>The "you own this one - Open / Create another" panel had no Back. Back (once added) then Continue skipped the panel and started a fresh sign-up on that number.</t>
+        </is>
+      </c>
+      <c r="F90" s="26" t="inlineStr">
+        <is>
+          <t>Back to the number; the panel returns.</t>
+        </is>
+      </c>
+      <c r="G90" s="26" t="inlineStr">
+        <is>
+          <t>4. Fix the bugs found (P1)</t>
+        </is>
+      </c>
+      <c r="H90" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I90" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push): Back shows on the panel; the last answer is kept and re-shown for the same confirmed number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="24" t="inlineStr">
+        <is>
+          <t>A-37</t>
+        </is>
+      </c>
+      <c r="B91" s="26" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="C91" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D91" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up email step</t>
+        </is>
+      </c>
+      <c r="E91" s="26" t="inlineStr">
+        <is>
+          <t>"This email already runs a company here - sign in instead" with no link to sign in (the header link is hidden on a phone).</t>
+        </is>
+      </c>
+      <c r="F91" s="26" t="inlineStr">
+        <is>
+          <t>A "Sign in instead" link carrying the number.</t>
+        </is>
+      </c>
+      <c r="G91" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H91" s="26" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I91" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 (awaiting push): link to /login?phone=&lt;number&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="24" t="inlineStr">
+        <is>
+          <t>A-38</t>
+        </is>
+      </c>
+      <c r="B92" s="26" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="C92" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D92" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up, every control</t>
+        </is>
+      </c>
+      <c r="E92" s="26" t="inlineStr">
+        <is>
+          <t>Clicked through and working: number checks, wrong/right code typed by hand, Change, Resend, multi-company picker, password sign-in (mixed case, spaces), 5-try lockout, Forgot password (send, again, back), reset links (missing, dead), old ?signup=1 link, bad invite link, demo panel open/back/seat, Privacy, Terms, Register links, consent ticks, website bad URL and manual path, interview typing/Back/mute/language, review flow steps, removing a sign-off rule, Tell Dex, Enter, Add people, Open from sign-up.</t>
+        </is>
+      </c>
+      <c r="F92" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G92" s="26" t="inlineStr">
+        <is>
+          <t>10. Polish (P3)</t>
+        </is>
+      </c>
+      <c r="H92" s="26" t="inlineStr">
+        <is>
+          <t>Works - no action</t>
+        </is>
+      </c>
+      <c r="I92" s="26" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="24" t="inlineStr">
+        <is>
+          <t>A-39</t>
+        </is>
+      </c>
+      <c r="B93" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C93" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D93" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in page, Email &amp; Password tab</t>
+        </is>
+      </c>
+      <c r="E93" s="26" t="inlineStr">
+        <is>
+          <t>Sign-up is mobile-only (nobody gets a password), but sign-in still offers an Email &amp; Password tab and a "Forgot your password?" link.</t>
+        </is>
+      </c>
+      <c r="F93" s="26" t="inlineStr">
+        <is>
+          <t>Remove the Email &amp; Password tab and the Forgot password link. The demo seat buttons keep working (they sign in behind the scenes, not through the tab).</t>
+        </is>
+      </c>
+      <c r="G93" s="26" t="inlineStr">
+        <is>
+          <t>9. Smaller product gaps (P2)</t>
+        </is>
+      </c>
+      <c r="H93" s="26" t="inlineStr">
+        <is>
+          <t>On hold - founder to confirm</t>
+        </is>
+      </c>
+      <c r="I93" s="26" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-08: sign-in is planned to be mobile number + code only. Do after the founder checks the older database. Do AFTER A-41.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="24" t="inlineStr">
+        <is>
+          <t>A-40</t>
+        </is>
+      </c>
+      <c r="B94" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C94" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D94" s="26" t="inlineStr">
+        <is>
+          <t>Owner added on Team without a mobile</t>
+        </is>
+      </c>
+      <c r="E94" s="26" t="inlineStr">
+        <is>
+          <t>An owner added or promoted on the Team page with no confirmed mobile is made to set an email and password (OwnerCredentialsGate), since otherwise they have no way back in.</t>
+        </is>
+      </c>
+      <c r="F94" s="26" t="inlineStr">
+        <is>
+          <t>They confirm their mobile by a texted code instead of setting a password.</t>
+        </is>
+      </c>
+      <c r="G94" s="26" t="inlineStr">
+        <is>
+          <t>9. Smaller product gaps (P2)</t>
+        </is>
+      </c>
+      <c r="H94" s="26" t="inlineStr">
+        <is>
+          <t>On hold - founder to confirm</t>
+        </is>
+      </c>
+      <c r="I94" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Founder 2026-10-08: sign-in is planned to be mobile number + code only. Do after the founder checks the older database. </t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="24" t="inlineStr">
+        <is>
+          <t>A-41</t>
+        </is>
+      </c>
+      <c r="B95" s="26" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="C95" s="26" t="inlineStr">
+        <is>
+          <t>Sign-in / sign-up</t>
+        </is>
+      </c>
+      <c r="D95" s="26" t="inlineStr">
+        <is>
+          <t>Live accounts with a password and no confirmed mobile</t>
+        </is>
+      </c>
+      <c r="E95" s="26" t="inlineStr">
+        <is>
+          <t>Removing the password tab would lock out anyone whose only way in is a password. Scratch DB has 21 accounts with a password; live not yet counted.</t>
+        </is>
+      </c>
+      <c r="F95" s="26" t="inlineStr">
+        <is>
+          <t>Count live accounts that have a password but no confirmed mobile, and get a confirmed mobile from each before switching the tab off.</t>
+        </is>
+      </c>
+      <c r="G95" s="26" t="inlineStr">
+        <is>
+          <t>9. Smaller product gaps (P2)</t>
+        </is>
+      </c>
+      <c r="H95" s="26" t="inlineStr">
+        <is>
+          <t>On hold - founder to confirm</t>
+        </is>
+      </c>
+      <c r="I95" s="26" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-08: sign-in is planned to be mobile number + code only. Do after the founder checks the older database. Prerequisite for A-39.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:I74"/>
+  <autoFilter ref="A4:I78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -11918,7 +11918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -11949,7 +11949,7 @@
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
         <is>
-          <t>Tally: P0 3 / P1 15 / P2 39 / P3 20 / Info 14 = 91 findings</t>
+          <t>Tally: P0 3 / P1 16 / P2 39 / P3 20 / Info 14 = 92 findings</t>
         </is>
       </c>
     </row>
@@ -12128,10 +12128,14 @@
       </c>
       <c r="H7" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I7" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I7" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): an unknown number gets the same "If this number has an account, we've texted it a code" (nothing sent; its code is just "Incorrect OTP"). A number in several companies gets ONE code; the companies are listed only after it is read back, then a 10-minute pick token opens the chosen one. "Start a company with this number" moved to the code screen. Verified in the browser.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="24" t="inlineStr">
@@ -12433,10 +12437,14 @@
       </c>
       <c r="H14" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I14" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): GET /signup/interview/{session_id} returns the waiting question (not the answers); the page saves the session id the moment the interview starts and resumes at that question. Verified: reload at Q4 reopened Q4.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
@@ -12523,10 +12531,14 @@
       </c>
       <c r="H16" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I16" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-08 in a735f5b: same bug as A-35 -- the review listed only the first 8 recurring tasks; it lists them all now.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
@@ -13231,10 +13243,14 @@
       </c>
       <c r="H32" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I32" s="26" t="inlineStr"/>
+          <t>On hold - founder to confirm</t>
+        </is>
+      </c>
+      <c r="I32" s="26" t="inlineStr">
+        <is>
+          <t>Founder 2026-10-08: sign-in to be mobile only. Tracked as A-39..A-41 (remove the tab after checking the older database).</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="24" t="inlineStr">
@@ -13403,10 +13419,14 @@
       </c>
       <c r="H36" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I36" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I36" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): Settings &gt; Company details &gt; On your invoices adds Payment terms (days) and Usual GST rate (used by the invoice builder; the server fills a missing due date from the terms), a logo upload printed at the top of the PDF, and a preview of the next invoice number. Already there before: GSTIN, address/state, prefix + FY numbering, bank/IFSC/UPI. Still not built: working days/holidays, leave types, notification preferences, integrations.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="24" t="inlineStr">
@@ -13665,10 +13685,14 @@
       </c>
       <c r="H42" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I42" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I42" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): adding a contact with the same name on the same side asks "There's already one called X" with Open it / Add anyway.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="24" t="inlineStr">
@@ -13708,10 +13732,14 @@
       </c>
       <c r="H43" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I43" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I43" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): GSTIN / Tax ID must be a 15-character GSTIN with a real state code, or a foreign tax number with its country prefix (GB123456789); stored upper-case without spaces.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="24" t="inlineStr">
@@ -13837,10 +13865,14 @@
       </c>
       <c r="H46" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I46" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I46" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): the move button shows a spinner and "Moving to &lt;stage&gt;..." (create already showed "Creating..."). Timing: ~4.7 s here is ~20 sequential DB round trips at ~220 ms from this laptop to the cloud DB; no AI in the path. Not re-measured on the live server.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="24" t="inlineStr">
@@ -14009,10 +14041,14 @@
       </c>
       <c r="H50" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I50" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I50" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): the extraction prompt (extraction.extract 1.3) is told today's date and returns the deadline date itself (due_on); services/voice.task_due_date uses it, else the day count, else no date. A task with no deadline stays undated and the review flags it "No date yet - set one". Live: "by Friday" said Thu 8 Oct -&gt; 9 Oct.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="24" t="inlineStr">
@@ -14545,10 +14581,14 @@
       </c>
       <c r="H62" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I62" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I62" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): documents.doc_extract 1.1 reads the counterparty GSTIN, taxable value and CGST/SGST/IGST; kept only when it adds up to the total. The GSTIN fills the supplier's empty tax id; with our GSTIN in Settings the bill's GST is input credit, kept out of stock cost (yarn 336 -&gt; 320/kg) and totalled on the Finance overview. The bill amount owed is unchanged.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="24" t="inlineStr">
@@ -14893,10 +14933,14 @@
       </c>
       <c r="H70" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I70" s="26" t="inlineStr"/>
+          <t>Works - no action</t>
+        </is>
+      </c>
+      <c r="I70" s="26" t="inlineStr">
+        <is>
+          <t>Founder decision 2026-10-09: by design. The Decision Desk (Voice Box capture) is for the managing side; team members have Ask. It uses the company's AI credits, so the owner decides who gets it (Settings &gt; Team &amp; access &gt; Teams &gt; Access). Stays off by default for non-owner teams.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="24" t="inlineStr">
@@ -14936,10 +14980,14 @@
       </c>
       <c r="H71" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I71" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I71" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): the invite start answers with the masked number only; verify reads the number from the invite itself. Verified: invited member signs in through the link.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="24" t="inlineStr">
@@ -16050,6 +16098,53 @@
       <c r="I95" s="26" t="inlineStr">
         <is>
           <t>Founder 2026-10-08: sign-in is planned to be mobile number + code only. Do after the founder checks the older database. Prerequisite for A-39.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="24" t="inlineStr">
+        <is>
+          <t>A-42</t>
+        </is>
+      </c>
+      <c r="B96" s="26" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C96" s="26" t="inlineStr">
+        <is>
+          <t>Desk</t>
+        </is>
+      </c>
+      <c r="D96" s="26" t="inlineStr">
+        <is>
+          <t>Desk on a short screen with decisions waiting</t>
+        </is>
+      </c>
+      <c r="E96" s="26" t="inlineStr">
+        <is>
+          <t>At 771x602 (the phone layout) the Desk crashed with "This panel couldn't render" (Maximum update depth exceeded in PhoneTabCard's row-fitting layout effects) once two decisions were pending; fine with none.</t>
+        </is>
+      </c>
+      <c r="F96" s="26" t="inlineStr">
+        <is>
+          <t>Converge the row measure; never loop.</t>
+        </is>
+      </c>
+      <c r="G96" s="26" t="inlineStr">
+        <is>
+          <t>4. Fix the bugs found (P1)</t>
+        </is>
+      </c>
+      <c r="H96" s="26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I96" s="26" t="inlineStr">
+        <is>
+          <t>Found 2026-10-09 while checking C-13; split out as its own task (not part of this batch).</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -14393,12 +14393,12 @@
       </c>
       <c r="H58" s="26" t="inlineStr">
         <is>
-          <t>Partly fixed</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="I58" s="26" t="inlineStr">
         <is>
-          <t>PARTLY FIXED 2026-10-08 (with F-04): the Finance AI context now carries payables_outstanding and payables_due (every unpaid purchase bill incl. those booked as stock). G-01 (Dex mixing receivables into "what we owe") still open.</t>
+          <t>FIXED 2026-10-09 (awaiting push): with F-04 the Finance AI context carries payables_outstanding / payables_due (bills booked as stock included); now /ledger/ask gets BOTH sides on every tab (it had no bill list on Revenue/Assets/Inventory), and ledger.ask 1.1 names which way each figure goes and forbids adding them. Golden set: evals/cases/finance.py (2 cases, pass replay AND live). Live on the scratch DB: "You owe Rs 1,68,000 to Sri Lakshmi Yarn Mills (SLY-4471, booked as inventory), due 5 Nov".</t>
         </is>
       </c>
     </row>
@@ -14714,10 +14714,14 @@
       </c>
       <c r="H65" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I65" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I65" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): routers/brain money_side() reads supplier vs customer from the question by code; supplier questions read purchase bills only (and an expenses plan becomes invoices), customer questions sales invoices only, and a question naming neither shows "Customers owe us" and "We owe suppliers" separately -- never one Outstanding. Rows say "Supplier bill (we owe)" / "Sales invoice (owed to us)". Live: Dex -&gt; "1 outstanding supplier bill totalling Rs 1,68,000 ... due 5 November 2026".</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="24" t="inlineStr">
@@ -16139,12 +16143,12 @@
       </c>
       <c r="H96" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="I96" s="26" t="inlineStr">
         <is>
-          <t>Found 2026-10-09 while checking C-13; split out as its own task (not part of this batch).</t>
+          <t>FIXED 2026-10-09 (awaiting push): Desk.js PhoneTabCard: tight is given back at most once per screen size (resize resets), and after it a shortfall must be seen afresh on new frames. Was: 9px untight / 45px tight, 45 &gt; 2x9, release, 9px, ask again in the same commit, forever. Checked 840x602, 360x640, 375x667, 390x844, 440x956 with 2 and 6 decisions, all three tabs.</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -13020,12 +13020,12 @@
       </c>
       <c r="H27" s="26" t="inlineStr">
         <is>
-          <t>Partly fixed</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="I27" s="26" t="inlineStr">
         <is>
-          <t>PARTLY FIXED with B-01: value-based sign-off stage (approval_delegate) now exists and is editable in Settings &gt; Operations. Per-stage gate conditions beyond the sign-off stage still open.</t>
+          <t>FIXED 2026-10-09 (awaiting push): a stage approval gate takes an optional value ("only above Rs X"): Settings &gt; Operations &gt; a stage &gt; Approval to leave this stage &gt; only above. At or under it the card leaves without the sign-off; over it, or with no value, it waits ("awaiting owner approval (needed above Rs 5,00,000)"). The card view says "it is over Rs X" or "No sign-off needed". The sign-up interview can set it too (generators.approval_rules 1.2, kind stage_signoff; golden case passes live). Live: 3L card moved on when its tasks were done; 7L and no-value cards waited.</t>
         </is>
       </c>
     </row>
@@ -15031,10 +15031,14 @@
       </c>
       <c r="H72" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I72" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I72" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): leave approver chain: reporting manager &gt; per-team mapping &gt; team from sign-up &gt; NEW: a lead in the person's own team who can approve leave &gt; a member of an HR/people team who can (HR teams start with leave_approve) &gt; anyone else who can &gt; the owner. Dates: "15-16 Oct" / "30 Oct - 2 Nov" on the Leave page and in the leave messages. Live: a sales member's leave went to Kavitha in HR; the page read "15-16 Oct".</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="24" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -13912,10 +13912,14 @@
       </c>
       <c r="H47" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I47" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I47" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): the Move-on box no longer closes a task that asks for proof without proof: the server carries it on with the card (counted as needs_proof) and the box shows "Needs proof - attach it on the task to close it" with Done off; "Set all: Done" skips it. Live: carried to Quality Check.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="24" t="inlineStr">
@@ -14088,10 +14092,14 @@
       </c>
       <c r="H51" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I51" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I51" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): services/voice.find_existing_work compares each proposed task with the open work already there -- on its card (the card's customer is implied, so "send the revised quotation to Northwind" matches "Send a preliminary quotation to the customer") and, more strictly, anywhere else. The review shows "Already on &lt;card&gt;: &lt;task&gt; - &lt;who&gt; - due &lt;date&gt;" with Use that task / Add as new; approving with Use updates that task's person and date, links the decision, and says "1 existing task updated" -- no twin. Live: quotation task moved to Fri 9 Oct, card still had two tasks.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="24" t="inlineStr">
@@ -14131,10 +14139,14 @@
       </c>
       <c r="H52" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I52" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I52" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): after Approve the window draws the approved decision from the answer itself (it waited for a re-read, seconds later, showing the old "ready for you" screen). "Approving..." shows while it works. Live: ~7 s on this laptop (cloud DB, ~220 ms a query), the window switched the moment it answered.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="24" t="inlineStr">
@@ -14260,10 +14272,14 @@
       </c>
       <c r="H55" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I55" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I55" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): routine set-up suggests a member of the team the routine is about (its category, else its words, via shared/roles.resolve_role); the owner only when that team has nobody. The picker says "from the &lt;team&gt; team". Live: loom routines -&gt; Murugan (Loom Production).</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="24" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -13157,10 +13157,14 @@
       </c>
       <c r="H30" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I30" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I30" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): sign-up now fills Company mobile (the number confirmed by code) and Company email (the company address if given, else the sign-up email). Region comes from the interview: the blueprint returns "region" only when the founder named a place, never a guess (evals region_from_interview -&gt; "Tiruppur" and niche_restaurant -&gt; blank, both pass live). Existing companies got mobile and email from the owner who signed up, blanks only (migration fill_company_contact_v1); their region stays for the owner to fill, as the interview wasn't stored.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="24" t="inlineStr">
@@ -13290,10 +13294,14 @@
       </c>
       <c r="H33" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I33" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I33" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): a new switch, "Manage people (add and edit members)" (staff_manage), is the people half of Manage Team on its own: add a member, correct their details, move them between teams, re-invite, bring back someone who left, see the attendance register. It never changes what anyone can open: with it alone the member follows their team's access, a team that itself has Manage Team is not offered, and someone who can Manage Team (or an owner) can't be edited (routers/team._refuse_beyond_people). Manage Team includes it. HR-named teams start with it; existing HR teams that approve leave got it (migration hr_teams_manage_people_v1). Company settings, teams, pipelines and access stay Manage Team's; removing someone stays the owner's. Live as Kavitha (HR): added Selvi to Production, renamed and moved her (200); own access, editing the owner and company settings refused (403).</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="24" t="inlineStr">
@@ -13333,10 +13341,14 @@
       </c>
       <c r="H34" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I34" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I34" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): when the only owner switches an area off for owners, the card asks first ("You're the only owner -- this hides Finance from you too. You can switch it back on here at any time") with Keep it on / Switch off for me too (server 409 only_owner_excludes_self until confirm_self). Turning areas back on never asks; with a co-owner it never asks. The way back always exists: the card is owner-only and owners always keep Manage team and Manage people (neither can be switched off). Live: 409, confirmed -&gt; /invoices 403 for the owner, switched back on -&gt; Finance again.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="24" t="inlineStr">
@@ -13556,10 +13568,14 @@
       </c>
       <c r="H39" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I39" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I39" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): the preview listed CRM struck through (read as "listed") and "Finance (upload only)" while the profile said "No access to ... Finance" -- both were true (HR holds Data Input, which opens Finance's upload inbox) but said differently. Add member and the profile now read one list (MenuList): the menus they will see, then "Not in their menus: CRM, Approvals." Live: HR preview and Kavitha's profile show the same seven menus.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="24" t="inlineStr">

--- a/docs/DecisionOS_Epic10_Testing.xlsx
+++ b/docs/DecisionOS_Epic10_Testing.xlsx
@@ -12085,10 +12085,14 @@
       </c>
       <c r="H6" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I6" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): sign-up keeps one extra browser-history entry and turns the browser's Back into the page's own Back (pages/onboarding/signupBack.js): a question goes to the one before, the code screen to the number, the language pick to the website step, an interview question to the previous one; the consent/website screens go to the last question. The finished review stays (stepping back would start a new interview and lose the answers). On the first question Back leaves sign-up, as before. Live: code screen -&gt; number -&gt; /login.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="24" t="inlineStr">
@@ -12175,10 +12179,14 @@
       </c>
       <c r="H8" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I8" s="26" t="inlineStr"/>
+          <t>Works - no action</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="inlineStr">
+        <is>
+          <t>Closed by design (founder, 2026-10-09): India-only mobile numbers stay; the market is India.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="24" t="inlineStr">
@@ -12218,10 +12226,14 @@
       </c>
       <c r="H9" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I9" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): a well-formed address on a domain that can't receive mail (e.g. .test) now reads "That email address can't receive mail — use one you check." (lib/api.js); other bad emails keep "does not look right".</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="24" t="inlineStr">
@@ -12261,10 +12273,14 @@
       </c>
       <c r="H10" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I10" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): "code" everywhere: Mobile number / Text me a code / Text it again; the server says "That code isn't right — 4 tries left.", "…and that was the last try — send yourself a new code", "That code has expired…", "Send yourself a code first." A number with no account counts down identically (services.otp.refuse_without_account, A-03 kept; parity test).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="24" t="inlineStr">
@@ -12304,10 +12320,14 @@
       </c>
       <c r="H11" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I11" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): login footer reads "Your team's work and decisions, in one place" (replaces the 24 Sep line "Workflow as an engine · Decision Desk · Dex").</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="24" t="inlineStr">
@@ -12578,10 +12598,14 @@
       </c>
       <c r="H17" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I17" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): the review's department and task pills wrap across each card (flex-wrap) instead of one per line.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="24" t="inlineStr">
@@ -12621,10 +12645,14 @@
       </c>
       <c r="H18" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I18" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): the interview prompt asks for the "why" said TO the founder (e.g. "So Dex knows what you check each week"); live sample: "So Dex knows your end-to-end production flow". Interview evals pass live.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
@@ -12664,10 +12692,14 @@
       </c>
       <c r="H19" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I19" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): founder's call: the interview language is for speaking comfortably only; everyone lands in the app in English. Register stores language "en" on the owner (AuthContext applies it), and the language pick says "This is only for the interview. DecisionOS itself opens in English."</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="24" t="inlineStr">
@@ -12754,10 +12786,14 @@
       </c>
       <c r="H21" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I21" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I21" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): the Desk example uses the company's own team ("Ask Sales &amp; Buyer Management to send the revised quote by Friday"), or a neutral line; the Dex chips no longer name Suresh, Priya, Anita or Krishna Garments.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="24" t="inlineStr">
@@ -13207,7 +13243,11 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="I31" s="26" t="inlineStr"/>
+      <c r="I31" s="26" t="inlineStr">
+        <is>
+          <t>Held with the WhatsApp backlog (founder, 2026-10-09).</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="24" t="inlineStr">
@@ -13388,10 +13428,14 @@
       </c>
       <c r="H35" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I35" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I35" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): team wording on every refusal ("There's already a Production team.", "Enter a team name.", "That team no longer exists — refresh the page.", "2 people are in this team. Move them…"); a rename to a name already used is refused too (it wasn't). Adding still confirms "Team \"X\" added".</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="24" t="inlineStr">
@@ -13615,10 +13659,14 @@
       </c>
       <c r="H40" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I40" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I40" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): a member with no manager reads "Reports to: Meera Iyer (owner) — no manager set", matching the tree; the Team page shows a legend for the dots (Active / Invite pending / Inactive) when anyone is not plain Active. Live on Rahul.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="24" t="inlineStr">
@@ -13658,10 +13706,14 @@
       </c>
       <c r="H41" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I41" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I41" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): Add member offers "Also email them the invite link" when an email is typed (sent with the existing mailer; best effort, the link is still shown); a duplicate email names the person when they are in this workspace ("That email is already Rahul Menon's in this workspace."), never someone in another company.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="24" t="inlineStr">
@@ -13795,10 +13847,14 @@
       </c>
       <c r="H44" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I44" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I44" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): a contact has trading terms: country, currency it pays in, payment terms (days), credit limit, and up to ten people at the firm (name, role, phone, email). The contact page shows them and its money in the contact's currency when all its invoices/payments are in it (desktop and phone), and warns over the credit limit. A new invoice for the contact takes its currency (export) and its payment terms for the due date. Live: Northwind UK Ltd, GBP, 60 days -&gt; invoice GBP due 8 Dec; page £1,500.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="24" t="inlineStr">
@@ -13838,10 +13894,14 @@
       </c>
       <c r="H45" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I45" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I45" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): the contact chip uses the company's word ("Buyer"); the CRM empty hint says "a buyer, a partner or a supplier" from the vocabulary; Delete sits on the contact page itself, asking the same "can't be undone" question (Keep them closes it).</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="24" t="inlineStr">
@@ -14202,10 +14262,14 @@
       </c>
       <c r="H53" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I53" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I53" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): note tags show as words ("About: Buyer terms") on the decision review, Company Brain and the Journal (lib/format.noteTag).</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="24" t="inlineStr">
@@ -14335,10 +14399,14 @@
       </c>
       <c r="H56" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I56" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I56" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): a pending member is listed "· not joined yet" and picking them says "Rahul hasn't joined yet — they'll see this once they do."; an empty title shows "Give the task a title" (larger, role=alert) and puts the caret back in it.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="24" t="inlineStr">
@@ -14660,10 +14728,14 @@
       </c>
       <c r="H63" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I63" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I63" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): no AI brief over an empty company ("Nothing to analyse yet — your first invoice, bill or expense starts the brief.", no AI call, not cached); one ask box (the hero's went — the AI panel's stays); KPI amounts break with &lt;wbr&gt; instead of zero-width spaces, so copying is plain digits; "Filed 1 invoice · 1 task" (and the activity log) with plurals and no zeros.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="24" t="inlineStr">
@@ -14793,10 +14865,14 @@
       </c>
       <c r="H66" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I66" s="26" t="inlineStr"/>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I66" s="26" t="inlineStr">
+        <is>
+          <t>FIXED 2026-10-09 (awaiting push): Finance scores only money already due (or paid): a first invoice not yet due leaves Finance out ("Nothing to score yet"), not 0/100; "Sales" is "Decisions" (approvals); the weakest area is always offered with a link (Execution -&gt; My Work, Finance -&gt; Finance, Decisions -&gt; Desk, Responsiveness -&gt; CRM), so a Fair score no longer says "Nothing urgent". Also fixed: the first-invoice step read decisions. Live: 68 Fair -&gt; "Execution is at 9 — Finish or re-date what is open".</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="24" t="inlineStr">
@@ -14879,10 +14955,14 @@
       </c>
       <c r="H68" s="26" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I68" s="26" t="inlineStr"/>
+          <t>Next phase</t>
+        </is>
+      </c>
+      <c r="I68" s="26" t="inlineStr">
+        <is>
+          <t>Moved to the next phase (founder, 2026-10-09). Open questions for then: leave year (Jan-Dec or Apr-Mar), block or flag over-allowance requests, defaults when no policy was given.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="24" t="inlineStr">
